--- a/Planilha_Mestre_Panorama_v5.1.xlsx
+++ b/Planilha_Mestre_Panorama_v5.1.xlsx
@@ -935,22 +935,22 @@
     <row r="7" ht="52" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
         <is>
-          <t>Mota Machado</t>
+          <t>Ergus</t>
         </is>
       </c>
       <c r="B7" s="12" t="inlineStr">
         <is>
-          <t>Edifício Bossa</t>
+          <t>Nexus Renascença</t>
         </is>
       </c>
       <c r="C7" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Calhau, São Luís - MA</t>
+          <t>Endereço não localizado, Renascença, São Luís - MA</t>
         </is>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
-          <t>Calhau</t>
+          <t>Renascença</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -960,17 +960,15 @@
       </c>
       <c r="F7" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Médio-alto</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Lançamento</t>
-        </is>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>60</v>
-      </c>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H7" s="12" t="n"/>
       <c r="I7" s="12" t="inlineStr">
         <is>
           <t>04/2026</t>
@@ -982,17 +980,17 @@
         </is>
       </c>
       <c r="K7" s="14" t="n">
-        <v>191</v>
+        <v>33</v>
       </c>
       <c r="L7" s="14" t="n">
-        <v>195</v>
+        <v>94</v>
       </c>
       <c r="M7" s="14" t="n">
-        <v>193</v>
+        <v>63.5</v>
       </c>
       <c r="N7" s="13" t="inlineStr">
         <is>
-          <t>4 suítes + vista mar</t>
+          <t>Studio a 2Q</t>
         </is>
       </c>
       <c r="O7" s="15" t="n"/>
@@ -1002,22 +1000,22 @@
       <c r="S7" s="16" t="n"/>
       <c r="T7" s="12" t="inlineStr">
         <is>
+          <t>site_oficial</t>
+        </is>
+      </c>
+      <c r="U7" s="12" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V7" s="12" t="inlineStr">
+        <is>
           <t>imprensa</t>
         </is>
       </c>
-      <c r="U7" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V7" s="12" t="inlineStr">
-        <is>
-          <t>imprensa</t>
-        </is>
-      </c>
       <c r="W7" s="12" t="inlineStr">
         <is>
-          <t>https://motamachado.com.br</t>
+          <t>https://www.ergus.com.br</t>
         </is>
       </c>
       <c r="X7" s="12" t="inlineStr">
@@ -1027,85 +1025,73 @@
       </c>
       <c r="Y7" s="13" t="inlineStr">
         <is>
-          <t>LANÇAMENTO ABRIL/2026 — evento oficial em 09/04/2026 (Frisson, MaHoje, Portal IN). 2 torres, 4 suítes, 191-195m², vista mar. Alto padrão/luxo. Mota Machado (CE) expandindo no NE, VGV 2025 R$350M.</t>
+          <t>Complexo 10mil m² multi-produto (residencial + comercial + Open Mall). Book local + site oficial.</t>
         </is>
       </c>
     </row>
     <row r="8" ht="52" customHeight="1">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Castelucci</t>
+          <t>Lua Nova</t>
         </is>
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>Vila Coimbra</t>
+          <t>Lagoon Residence</t>
         </is>
       </c>
       <c r="C8" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Araçagi, São Luís - MA</t>
+          <t>Endereço não localizado, Santo Amaro, São Luís - MA</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
         <is>
-          <t>Araçagi</t>
+          <t>Santo Amaro</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
-          <t>Médio</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="6" t="inlineStr">
         <is>
-          <t>Lançamento</t>
+          <t>Em comercialização</t>
         </is>
       </c>
       <c r="H8" s="6" t="n"/>
       <c r="I8" s="6" t="inlineStr">
         <is>
-          <t>03/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>03/2029</t>
-        </is>
-      </c>
-      <c r="K8" s="8" t="n">
-        <v>124.63</v>
-      </c>
-      <c r="L8" s="8" t="n">
-        <v>124.63</v>
-      </c>
-      <c r="M8" s="8" t="n">
-        <v>124.63</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K8" s="8" t="n"/>
+      <c r="L8" s="8" t="n"/>
+      <c r="M8" s="8" t="n"/>
       <c r="N8" s="7" t="inlineStr">
         <is>
-          <t>Casa 124,63 m² (terreno 164-204 m²)</t>
-        </is>
-      </c>
-      <c r="O8" s="9" t="n">
-        <v>1019834</v>
-      </c>
-      <c r="P8" s="9" t="n">
-        <v>1081967</v>
-      </c>
-      <c r="Q8" s="9" t="n">
-        <v>8432.16320308112</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O8" s="9" t="n"/>
+      <c r="P8" s="9" t="n"/>
+      <c r="Q8" s="9" t="n"/>
       <c r="R8" s="9" t="n"/>
       <c r="S8" s="10" t="n"/>
       <c r="T8" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U8" s="6" t="inlineStr">
@@ -1115,153 +1101,153 @@
       </c>
       <c r="V8" s="6" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W8" s="6" t="inlineStr">
         <is>
-          <t>https://construtoracastelucci.com.br</t>
+          <t>https://construtoraluanova.com.br</t>
         </is>
       </c>
       <c r="X8" s="6" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y8" s="7" t="inlineStr">
         <is>
-          <t>Tabela LANÇAMENTO 03/2026. Parceria Castelucci + Grupo Coimbra Alves. ~36-41 casas no Araçagi (numeração até casa 41, várias agrupadas: 02-17, 36-38, 39-40). Área construída UNIFORME 124,63 m². Terreno varia 164-204 m². Ticket à vista R$ 1.019.834 (casa 21) a R$ 1.081.967 (casa 41) — VARIAÇÃO POR TAMANHO DE TERRENO, não por área construída. Avaliação: R$ 915.000. Pagamento: 24m IPCA+0,49% / 36m IPCA+1,49% / Caixa. Lazer privativa não integrada ao preço. Paulo Castelucci (CEO) em entrevista à Mirante FM. Patrocínio Imob Summit 2026.</t>
+          <t>Residência no Santo Amaro — região com oferta crescente de médio padrão.</t>
         </is>
       </c>
     </row>
     <row r="9" ht="52" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Mota Machado</t>
         </is>
       </c>
       <c r="B9" s="12" t="inlineStr">
         <is>
-          <t>Dom Lucas</t>
+          <t>Edifício Bossa</t>
         </is>
       </c>
       <c r="C9" s="13" t="inlineStr">
         <is>
-          <t>Tv. Boa Esperança, 101 - Cantinho do Céu, São Luís - MA, 65074-030</t>
+          <t>Endereço não localizado, Calhau, São Luís - MA</t>
         </is>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
-          <t>Cantinho do Céu</t>
+          <t>Calhau</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="n"/>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="H9" s="12" t="n">
+        <v>60</v>
+      </c>
       <c r="I9" s="12" t="inlineStr">
         <is>
-          <t>02/2026</t>
+          <t>04/2026</t>
         </is>
       </c>
       <c r="J9" s="12" t="inlineStr">
         <is>
-          <t>01/2029</t>
+          <t>—</t>
         </is>
       </c>
       <c r="K9" s="14" t="n">
-        <v>100.35</v>
+        <v>191</v>
       </c>
       <c r="L9" s="14" t="n">
-        <v>145.78</v>
+        <v>195</v>
       </c>
       <c r="M9" s="14" t="n">
-        <v>123.065</v>
+        <v>193</v>
       </c>
       <c r="N9" s="13" t="inlineStr">
         <is>
-          <t>Casa 3 dorm (1 suíte) + 2 vagas</t>
-        </is>
-      </c>
-      <c r="O9" s="15" t="n">
-        <v>835000</v>
-      </c>
-      <c r="P9" s="15" t="n">
-        <v>851000</v>
-      </c>
-      <c r="Q9" s="15" t="n">
-        <v>6850.038597489131</v>
-      </c>
+          <t>4 suítes + vista mar</t>
+        </is>
+      </c>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="15" t="n"/>
+      <c r="Q9" s="15" t="n"/>
       <c r="R9" s="15" t="n"/>
       <c r="S9" s="16" t="n"/>
       <c r="T9" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="U9" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V9" s="12" t="inlineStr">
         <is>
-          <t>interno</t>
-        </is>
-      </c>
-      <c r="W9" s="12" t="inlineStr"/>
+          <t>imprensa</t>
+        </is>
+      </c>
+      <c r="W9" s="12" t="inlineStr">
+        <is>
+          <t>https://motamachado.com.br</t>
+        </is>
+      </c>
       <c r="X9" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y9" s="13" t="inlineStr">
         <is>
-          <t>Condomínio horizontal (sobrados). Área casa 100,35 m² + terreno 136-146 m². ~38 casas. Lazer: campo society, piscina, deck, salão, gourmet, petplay, playground. Muitas unidades VENDIDAS. Entrega DEZ/2026. Ticket R$ 835-851k. R$/m² construção ~R$ 8.400. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>LANÇAMENTO ABRIL/2026 — evento oficial em 09/04/2026 (Frisson, MaHoje, Portal IN). 2 torres, 4 suítes, 191-195m², vista mar. Alto padrão/luxo. Mota Machado (CE) expandindo no NE, VGV 2025 R$350M.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="52" customHeight="1">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Castelucci</t>
         </is>
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>Landscape</t>
+          <t>Vila Coimbra</t>
         </is>
       </c>
       <c r="C10" s="7" t="inlineStr">
         <is>
-          <t>Avenida dos Holandeses, S/N, Calhau, São Luís - MA</t>
+          <t>Endereço não localizado, Araçagi, São Luís - MA</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>Calhau</t>
+          <t>Araçagi</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Médio</t>
         </is>
       </c>
       <c r="G10" s="6" t="inlineStr">
@@ -1269,48 +1255,42 @@
           <t>Lançamento</t>
         </is>
       </c>
-      <c r="H10" s="6" t="n">
-        <v>95</v>
-      </c>
+      <c r="H10" s="6" t="n"/>
       <c r="I10" s="6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>03/2026</t>
         </is>
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>09/2029</t>
+          <t>03/2029</t>
         </is>
       </c>
       <c r="K10" s="8" t="n">
-        <v>88</v>
+        <v>124.63</v>
       </c>
       <c r="L10" s="8" t="n">
-        <v>103</v>
+        <v>124.63</v>
       </c>
       <c r="M10" s="8" t="n">
-        <v>95.5</v>
+        <v>124.63</v>
       </c>
       <c r="N10" s="7" t="inlineStr">
         <is>
-          <t>3 suítes</t>
+          <t>Casa 124,63 m² (terreno 164-204 m²)</t>
         </is>
       </c>
       <c r="O10" s="9" t="n">
-        <v>1200000</v>
+        <v>1019834</v>
       </c>
       <c r="P10" s="9" t="n">
-        <v>1500000</v>
+        <v>1081967</v>
       </c>
       <c r="Q10" s="9" t="n">
-        <v>14136.12565445026</v>
-      </c>
-      <c r="R10" s="9" t="n">
-        <v>128250000</v>
-      </c>
-      <c r="S10" s="10" t="n">
-        <v>0.4526315789473684</v>
-      </c>
+        <v>8432.16320308112</v>
+      </c>
+      <c r="R10" s="9" t="n"/>
+      <c r="S10" s="10" t="n"/>
       <c r="T10" s="6" t="inlineStr">
         <is>
           <t>tabela_local</t>
@@ -1318,49 +1298,49 @@
       </c>
       <c r="U10" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V10" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>book</t>
         </is>
       </c>
       <c r="W10" s="6" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://construtoracastelucci.com.br</t>
         </is>
       </c>
       <c r="X10" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="Y10" s="7" t="inlineStr">
         <is>
-          <t>Tabela 04/2026 marcada 'pré-lançamento'. Fonte web confirma lançamento 2026. Duplex cobertura 123-143m².</t>
+          <t>Tabela LANÇAMENTO 03/2026. Parceria Castelucci + Grupo Coimbra Alves. ~36-41 casas no Araçagi (numeração até casa 41, várias agrupadas: 02-17, 36-38, 39-40). Área construída UNIFORME 124,63 m². Terreno varia 164-204 m². Ticket à vista R$ 1.019.834 (casa 21) a R$ 1.081.967 (casa 41) — VARIAÇÃO POR TAMANHO DE TERRENO, não por área construída. Avaliação: R$ 915.000. Pagamento: 24m IPCA+0,49% / 36m IPCA+1,49% / Caixa. Lazer privativa não integrada ao preço. Paulo Castelucci (CEO) em entrevista à Mirante FM. Patrocínio Imob Summit 2026.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="52" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
         <is>
-          <t>Niágara</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B11" s="12" t="inlineStr">
         <is>
-          <t>ORO Ponta d'Areia</t>
+          <t>Landscape</t>
         </is>
       </c>
       <c r="C11" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Avenida dos Holandeses, S/N, Calhau, São Luís - MA</t>
         </is>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Calhau</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -1378,42 +1358,48 @@
           <t>Lançamento</t>
         </is>
       </c>
-      <c r="H11" s="12" t="n"/>
+      <c r="H11" s="12" t="n">
+        <v>95</v>
+      </c>
       <c r="I11" s="12" t="inlineStr">
         <is>
-          <t>~2026 ⚠ T-36</t>
+          <t>03/2026</t>
         </is>
       </c>
       <c r="J11" s="12" t="inlineStr">
         <is>
-          <t>~2029</t>
+          <t>09/2029</t>
         </is>
       </c>
       <c r="K11" s="14" t="n">
-        <v>80.31999999999999</v>
+        <v>88</v>
       </c>
       <c r="L11" s="14" t="n">
-        <v>160.64</v>
+        <v>103</v>
       </c>
       <c r="M11" s="14" t="n">
-        <v>120.48</v>
+        <v>95.5</v>
       </c>
       <c r="N11" s="13" t="inlineStr">
         <is>
-          <t>2-4 suítes</t>
+          <t>3 suítes</t>
         </is>
       </c>
       <c r="O11" s="15" t="n">
-        <v>1000000</v>
+        <v>1200000</v>
       </c>
       <c r="P11" s="15" t="n">
-        <v>2600000</v>
+        <v>1500000</v>
       </c>
       <c r="Q11" s="15" t="n">
-        <v>14940.2390438247</v>
-      </c>
-      <c r="R11" s="15" t="n"/>
-      <c r="S11" s="16" t="n"/>
+        <v>14136.12565445026</v>
+      </c>
+      <c r="R11" s="15" t="n">
+        <v>128250000</v>
+      </c>
+      <c r="S11" s="16" t="n">
+        <v>0.4526315789473684</v>
+      </c>
       <c r="T11" s="12" t="inlineStr">
         <is>
           <t>tabela_local</t>
@@ -1421,17 +1407,17 @@
       </c>
       <c r="U11" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V11" s="12" t="inlineStr">
         <is>
-          <t>estimativa_T-36</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W11" s="12" t="inlineStr">
         <is>
-          <t>https://www.niagara-imoveis.com.br</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="X11" s="12" t="inlineStr">
@@ -1441,29 +1427,29 @@
       </c>
       <c r="Y11" s="13" t="inlineStr">
         <is>
-          <t>Tabela JAN/26 é matriz por posição (não espelha estoque). Duplex cobertura 160m². Parcelamento 48m pós-assinatura.</t>
+          <t>Tabela 04/2026 marcada 'pré-lançamento'. Fonte web confirma lançamento 2026. Duplex cobertura 123-143m².</t>
         </is>
       </c>
     </row>
     <row r="12" ht="52" customHeight="1">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>Canopus</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>Village Del Ville II</t>
+          <t>Dom Lucas</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>Tv. Boa Esperança, 101 - Cantinho do Céu, São Luís - MA, 65074-030</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Cantinho do Céu</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1473,93 +1459,101 @@
       </c>
       <c r="F12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Médio-alto</t>
         </is>
       </c>
       <c r="G12" s="6" t="inlineStr">
         <is>
-          <t>Lançamento</t>
+          <t>Em comercialização</t>
         </is>
       </c>
       <c r="H12" s="6" t="n"/>
       <c r="I12" s="6" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>02/2026</t>
         </is>
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
+          <t>01/2029</t>
+        </is>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>100.35</v>
+      </c>
+      <c r="L12" s="8" t="n">
+        <v>145.78</v>
+      </c>
+      <c r="M12" s="8" t="n">
+        <v>123.065</v>
+      </c>
       <c r="N12" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O12" s="9" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
+          <t>Casa 3 dorm (1 suíte) + 2 vagas</t>
+        </is>
+      </c>
+      <c r="O12" s="9" t="n">
+        <v>835000</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>851000</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>6850.038597489131</v>
+      </c>
       <c r="R12" s="9" t="n"/>
       <c r="S12" s="10" t="n"/>
       <c r="T12" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U12" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="V12" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
-        </is>
-      </c>
-      <c r="W12" s="6" t="inlineStr">
-        <is>
-          <t>https://canopusconstrucoes.com.br</t>
-        </is>
-      </c>
+          <t>interno</t>
+        </is>
+      </c>
+      <c r="W12" s="6" t="inlineStr"/>
       <c r="X12" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y12" s="7" t="inlineStr">
         <is>
-          <t>Série Village (estratégia de marca clara). Imirante 31/10/2025. Confirmar tipologia/ticket via site+IG.</t>
+          <t>Condomínio horizontal (sobrados). Área casa 100,35 m² + terreno 136-146 m². ~38 casas. Lazer: campo society, piscina, deck, salão, gourmet, petplay, playground. Muitas unidades VENDIDAS. Entrega DEZ/2026. Ticket R$ 835-851k. R$/m² construção ~R$ 8.400. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="13" ht="52" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>Canopus</t>
+          <t>MB Engenharia</t>
         </is>
       </c>
       <c r="B13" s="12" t="inlineStr">
         <is>
-          <t>Village Prime Eldorado</t>
+          <t>Condomínio Prime Cohama</t>
         </is>
       </c>
       <c r="C13" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Jardim Eldorado, São Luís - MA</t>
+          <t>Endereço não localizado, Cohama, São Luís - MA</t>
         </is>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
-          <t>Jardim Eldorado</t>
+          <t>Cohama</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -1569,13 +1563,15 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Lançamento</t>
-        </is>
-      </c>
-      <c r="H13" s="12" t="n"/>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H13" s="12" t="n">
+        <v>22</v>
+      </c>
       <c r="I13" s="12" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>01/2026</t>
         </is>
       </c>
       <c r="J13" s="12" t="inlineStr">
@@ -1583,12 +1579,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K13" s="14" t="n"/>
-      <c r="L13" s="14" t="n"/>
-      <c r="M13" s="14" t="n"/>
+      <c r="K13" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="L13" s="14" t="n">
+        <v>140</v>
+      </c>
+      <c r="M13" s="14" t="n">
+        <v>140</v>
+      </c>
       <c r="N13" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Casas duplex</t>
         </is>
       </c>
       <c r="O13" s="15" t="n"/>
@@ -1613,7 +1615,7 @@
       </c>
       <c r="W13" s="12" t="inlineStr">
         <is>
-          <t>https://canopusconstrucoes.com.br</t>
+          <t>https://www.instagram.com/mbengenharia.br/</t>
         </is>
       </c>
       <c r="X13" s="12" t="inlineStr">
@@ -1623,39 +1625,39 @@
       </c>
       <c r="Y13" s="13" t="inlineStr">
         <is>
-          <t>Canopus em movimento forte no Eldorado. Fonte: Imirante 31/10/2025.</t>
+          <t>22 casas duplex 140m² — produto horizontal diferenciado. Pré-lançamento anunciado 2023, hoje em comercialização.</t>
         </is>
       </c>
     </row>
     <row r="14" ht="52" customHeight="1">
       <c r="A14" s="5" t="inlineStr">
         <is>
-          <t>Canopus</t>
+          <t>Niágara</t>
         </is>
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>Village Reserva II</t>
+          <t>ORO Ponta d'Areia</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G14" s="6" t="inlineStr">
@@ -1666,45 +1668,57 @@
       <c r="H14" s="6" t="n"/>
       <c r="I14" s="6" t="inlineStr">
         <is>
-          <t>10/2025</t>
+          <t>01/2026 ⚠ T-36</t>
         </is>
       </c>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="8" t="n"/>
-      <c r="M14" s="8" t="n"/>
+          <t>~2029</t>
+        </is>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>80.31999999999999</v>
+      </c>
+      <c r="L14" s="8" t="n">
+        <v>160.64</v>
+      </c>
+      <c r="M14" s="8" t="n">
+        <v>120.48</v>
+      </c>
       <c r="N14" s="7" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O14" s="9" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
+          <t>2-4 suítes</t>
+        </is>
+      </c>
+      <c r="O14" s="9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>2600000</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>14940.2390438247</v>
+      </c>
       <c r="R14" s="9" t="n"/>
       <c r="S14" s="10" t="n"/>
       <c r="T14" s="6" t="inlineStr">
         <is>
+          <t>tabela_local</t>
+        </is>
+      </c>
+      <c r="U14" s="6" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U14" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="V14" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>estimativa_T-36</t>
         </is>
       </c>
       <c r="W14" s="6" t="inlineStr">
         <is>
-          <t>https://canopusconstrucoes.com.br</t>
+          <t>https://www.niagara-imoveis.com.br</t>
         </is>
       </c>
       <c r="X14" s="6" t="inlineStr">
@@ -1714,39 +1728,39 @@
       </c>
       <c r="Y14" s="7" t="inlineStr">
         <is>
-          <t>1 dos 3 novos lançamentos Canopus anunciados em 31/10/2025 (Imirante). SEM tabela ou book mapeado.</t>
+          <t>Tabela JAN/26 é matriz por posição (não espelha estoque). Duplex cobertura 160m². Parcelamento 48m pós-assinatura.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t>Sá Cavalcante</t>
+          <t>Canopus</t>
         </is>
       </c>
       <c r="B15" s="12" t="inlineStr">
         <is>
-          <t>Reserva Península</t>
+          <t>Village Del Ville II</t>
         </is>
       </c>
       <c r="C15" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia (Península), São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -1780,7 +1794,7 @@
       <c r="S15" s="16" t="n"/>
       <c r="T15" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U15" s="12" t="inlineStr">
@@ -1790,12 +1804,12 @@
       </c>
       <c r="V15" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W15" s="12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/sacavalcantema/</t>
+          <t>https://canopusconstrucoes.com.br</t>
         </is>
       </c>
       <c r="X15" s="12" t="inlineStr">
@@ -1805,69 +1819,63 @@
       </c>
       <c r="Y15" s="13" t="inlineStr">
         <is>
-          <t>Lançamento Sá Cavalcante out/2025. Estande 'Casa Sal' na Península. 'Os espaços conversam...' — narrativa de estilo de vida.</t>
+          <t>Série Village (estratégia de marca clara). Imirante 31/10/2025. Confirmar tipologia/ticket via site+IG.</t>
         </is>
       </c>
     </row>
     <row r="16" ht="52" customHeight="1">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>Ergus</t>
+          <t>Canopus</t>
         </is>
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>Zion Ponta d'Areia</t>
+          <t>Village Prime Eldorado</t>
         </is>
       </c>
       <c r="C16" s="7" t="inlineStr">
         <is>
-          <t>Rua Aziz Heluy, S/N, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, Jardim Eldorado, São Luís - MA</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Jardim Eldorado</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="6" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
+          <t>Lançamento</t>
         </is>
       </c>
       <c r="H16" s="6" t="n"/>
       <c r="I16" s="6" t="inlineStr">
         <is>
-          <t>09/2025</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>12/2026</t>
-        </is>
-      </c>
-      <c r="K16" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="L16" s="8" t="n">
-        <v>148</v>
-      </c>
-      <c r="M16" s="8" t="n">
-        <v>148</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K16" s="8" t="n"/>
+      <c r="L16" s="8" t="n"/>
+      <c r="M16" s="8" t="n"/>
       <c r="N16" s="7" t="inlineStr">
         <is>
-          <t>4 suítes + 3 vagas</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O16" s="9" t="n"/>
@@ -1877,7 +1885,7 @@
       <c r="S16" s="10" t="n"/>
       <c r="T16" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U16" s="6" t="inlineStr">
@@ -1887,12 +1895,12 @@
       </c>
       <c r="V16" s="6" t="inlineStr">
         <is>
-          <t>treinamento_corretor</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W16" s="6" t="inlineStr">
         <is>
-          <t>https://www.ergus.com.br</t>
+          <t>https://canopusconstrucoes.com.br</t>
         </is>
       </c>
       <c r="X16" s="6" t="inlineStr">
@@ -1902,106 +1910,88 @@
       </c>
       <c r="Y16" s="7" t="inlineStr">
         <is>
-          <t>2 torres, 2 aptos/andar, 15 andares. Elevadores triplos. Treinamento corretor 12/09/2025 confirma lançamento comercial ~set/2025.</t>
+          <t>Canopus em movimento forte no Eldorado. Fonte: Imirante 31/10/2025.</t>
         </is>
       </c>
     </row>
     <row r="17" ht="52" customHeight="1">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Canopus</t>
         </is>
       </c>
       <c r="B17" s="12" t="inlineStr">
         <is>
-          <t>Studio Design 7 Península</t>
+          <t>Village Reserva II</t>
         </is>
       </c>
       <c r="C17" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H17" s="12" t="n">
-        <v>125</v>
-      </c>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="H17" s="12" t="n"/>
       <c r="I17" s="12" t="inlineStr">
         <is>
-          <t>04/2025 ⚠ T-36</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="J17" s="12" t="inlineStr">
         <is>
-          <t>04/2028</t>
-        </is>
-      </c>
-      <c r="K17" s="14" t="n">
-        <v>43</v>
-      </c>
-      <c r="L17" s="14" t="n">
-        <v>64</v>
-      </c>
-      <c r="M17" s="14" t="n">
-        <v>53.5</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K17" s="14" t="n"/>
+      <c r="L17" s="14" t="n"/>
+      <c r="M17" s="14" t="n"/>
       <c r="N17" s="13" t="inlineStr">
         <is>
-          <t>Studio / 1Q</t>
-        </is>
-      </c>
-      <c r="O17" s="15" t="n">
-        <v>710000</v>
-      </c>
-      <c r="P17" s="15" t="n">
-        <v>1000000</v>
-      </c>
-      <c r="Q17" s="15" t="n">
-        <v>15981.30841121495</v>
-      </c>
-      <c r="R17" s="15" t="n">
-        <v>106875000</v>
-      </c>
-      <c r="S17" s="16" t="n">
-        <v>0.736</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="15" t="n"/>
+      <c r="S17" s="16" t="n"/>
       <c r="T17" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U17" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V17" s="12" t="inlineStr">
         <is>
-          <t>estimativa_T-36</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W17" s="12" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://canopusconstrucoes.com.br</t>
         </is>
       </c>
       <c r="X17" s="12" t="inlineStr">
@@ -2011,29 +2001,29 @@
       </c>
       <c r="Y17" s="13" t="inlineStr">
         <is>
-          <t>33 de 125 aptos à venda. ≈74% vendido em ~18 meses. Forte velocidade em compactos.</t>
+          <t>1 dos 3 novos lançamentos Canopus anunciados em 31/10/2025 (Imirante). SEM tabela ou book mapeado.</t>
         </is>
       </c>
     </row>
     <row r="18" ht="52" customHeight="1">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>Hiali</t>
+          <t>Sá Cavalcante</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>Le Noir</t>
+          <t>Reserva Península</t>
         </is>
       </c>
       <c r="C18" s="7" t="inlineStr">
         <is>
-          <t>Rua Osires, 05, Renascença II, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia (Península), São Luís - MA</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>Renascença II</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E18" s="6" t="inlineStr">
@@ -2051,87 +2041,75 @@
           <t>Lançamento</t>
         </is>
       </c>
-      <c r="H18" s="6" t="n">
-        <v>25</v>
-      </c>
+      <c r="H18" s="6" t="n"/>
       <c r="I18" s="6" t="inlineStr">
         <is>
-          <t>04/2025</t>
+          <t>10/2025</t>
         </is>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>12/2027</t>
-        </is>
-      </c>
-      <c r="K18" s="8" t="n">
-        <v>49.74</v>
-      </c>
-      <c r="L18" s="8" t="n">
-        <v>62.62</v>
-      </c>
-      <c r="M18" s="8" t="n">
-        <v>56.18</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K18" s="8" t="n"/>
+      <c r="L18" s="8" t="n"/>
+      <c r="M18" s="8" t="n"/>
       <c r="N18" s="7" t="inlineStr">
         <is>
-          <t>Studios e 1-2 dorm (compactos premium)</t>
-        </is>
-      </c>
-      <c r="O18" s="9" t="n">
-        <v>710000</v>
-      </c>
-      <c r="P18" s="9" t="n">
-        <v>870000</v>
-      </c>
-      <c r="Q18" s="9" t="n">
-        <v>14061.94375222499</v>
-      </c>
-      <c r="R18" s="9" t="n">
-        <v>19750000</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="9" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
       <c r="S18" s="10" t="n"/>
       <c r="T18" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U18" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V18" s="6" t="inlineStr">
         <is>
-          <t>memorial</t>
-        </is>
-      </c>
-      <c r="W18" s="6" t="inlineStr"/>
+          <t>site_oficial</t>
+        </is>
+      </c>
+      <c r="W18" s="6" t="inlineStr">
+        <is>
+          <t>https://www.instagram.com/sacavalcantema/</t>
+        </is>
+      </c>
       <c r="X18" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y18" s="7" t="inlineStr">
         <is>
-          <t>Parceria Hiali + Silveira Inc. Compactos premium: 49,74 / 58,91 / 62,62 m². 5 pavimentos tipo × 5 aptos/andar = ~25 unidades. Entrega DEZ/2027. Ticket R$ 710-870k. R$/m² méd R$ 13.810. Memorial R.09/25.101 registrado 17/04/2025 no 1º RI São Luís. Foco em mercado jovem / investidor. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Lançamento Sá Cavalcante out/2025. Estande 'Casa Sal' na Península. 'Os espaços conversam...' — narrativa de estilo de vida.</t>
         </is>
       </c>
     </row>
     <row r="19" ht="52" customHeight="1">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B19" s="12" t="inlineStr">
         <is>
-          <t>Giardino Residenza Torre Fiore</t>
+          <t>Wave Residence</t>
         </is>
       </c>
       <c r="C19" s="13" t="inlineStr">
         <is>
-          <t>Ponta do Farol, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta do Farol, São Luís - MA</t>
         </is>
       </c>
       <c r="D19" s="12" t="inlineStr">
@@ -2146,55 +2124,55 @@
       </c>
       <c r="F19" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Últimas unidades</t>
+          <t>Em comercialização</t>
         </is>
       </c>
       <c r="H19" s="12" t="n">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="I19" s="12" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="J19" s="12" t="inlineStr">
         <is>
-          <t>12/2029</t>
+          <t>03/2029</t>
         </is>
       </c>
       <c r="K19" s="14" t="n">
-        <v>110.77</v>
+        <v>293.69</v>
       </c>
       <c r="L19" s="14" t="n">
-        <v>128.37</v>
+        <v>293.69</v>
       </c>
       <c r="M19" s="14" t="n">
-        <v>119.57</v>
+        <v>293.69</v>
       </c>
       <c r="N19" s="13" t="inlineStr">
         <is>
-          <t>2 suítes + 2 semi-suítes OU 3 suítes, varanda, lavabo, 3 vagas, depósito</t>
+          <t>4 suítes</t>
         </is>
       </c>
       <c r="O19" s="15" t="n">
-        <v>1838492</v>
+        <v>5500000</v>
       </c>
       <c r="P19" s="15" t="n">
-        <v>2032939</v>
+        <v>5800000</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <v>16188.97298653509</v>
+        <v>19237.97201130444</v>
       </c>
       <c r="R19" s="15" t="n">
-        <v>87107197.5</v>
+        <v>169500000</v>
       </c>
       <c r="S19" s="16" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8333333333333334</v>
       </c>
       <c r="T19" s="12" t="inlineStr">
         <is>
@@ -2208,44 +2186,44 @@
       </c>
       <c r="V19" s="12" t="inlineStr">
         <is>
-          <t>memorial</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W19" s="12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alfaengenhariama/</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="X19" s="12" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y19" s="13" t="inlineStr">
         <is>
-          <t>Torre NORTE do Giardino. 15 pav × 3 un = 45 unidades. 3 tipologias: 127,30 / 128,37 / 110,77 m². Tabela MAR/2026: 6 unidades disponíveis (1001/701/201/101 da coluna 127m², 102 da coluna 128m², 1403 da coluna 110m²) = ~13% estoque, 87% VENDIDO → Últimas unidades. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL. Endereço Alfa: Rua Peixe Pedra, Qd 12 lote 04, Calhau.</t>
+          <t>Evento de apresentação oficial 2024. 5 de 30 à venda. ≈83% vendido. Piscina privativa na varanda.</t>
         </is>
       </c>
     </row>
     <row r="20" ht="52" customHeight="1">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Ergus</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>Giardino Residenza Torre Luce</t>
+          <t>Zion Ponta d'Areia</t>
         </is>
       </c>
       <c r="C20" s="7" t="inlineStr">
         <is>
-          <t>Ponta do Farol, São Luís - MA</t>
+          <t>Rua Aziz Heluy, S/N, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>Ponta do Farol</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
@@ -2260,101 +2238,89 @@
       </c>
       <c r="G20" s="6" t="inlineStr">
         <is>
-          <t>Últimas unidades</t>
-        </is>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>60</v>
-      </c>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H20" s="6" t="n"/>
       <c r="I20" s="6" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>09/2025</t>
         </is>
       </c>
       <c r="J20" s="6" t="inlineStr">
         <is>
-          <t>12/2029</t>
+          <t>12/2026</t>
         </is>
       </c>
       <c r="K20" s="8" t="n">
-        <v>93.18000000000001</v>
+        <v>148</v>
       </c>
       <c r="L20" s="8" t="n">
-        <v>101.31</v>
+        <v>148</v>
       </c>
       <c r="M20" s="8" t="n">
-        <v>97.245</v>
+        <v>148</v>
       </c>
       <c r="N20" s="7" t="inlineStr">
         <is>
-          <t>3 suítes, varanda, lavabo, 2 vagas, depósito</t>
-        </is>
-      </c>
-      <c r="O20" s="9" t="n">
-        <v>1442168</v>
-      </c>
-      <c r="P20" s="9" t="n">
-        <v>1595303</v>
-      </c>
-      <c r="Q20" s="9" t="n">
-        <v>15617.62044321045</v>
-      </c>
-      <c r="R20" s="9" t="n">
-        <v>91124130</v>
-      </c>
-      <c r="S20" s="10" t="n">
-        <v>0.9166666666666666</v>
-      </c>
+          <t>4 suítes + 3 vagas</t>
+        </is>
+      </c>
+      <c r="O20" s="9" t="n"/>
+      <c r="P20" s="9" t="n"/>
+      <c r="Q20" s="9" t="n"/>
+      <c r="R20" s="9" t="n"/>
+      <c r="S20" s="10" t="n"/>
       <c r="T20" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U20" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V20" s="6" t="inlineStr">
         <is>
-          <t>memorial</t>
+          <t>treinamento_corretor</t>
         </is>
       </c>
       <c r="W20" s="6" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/alfaengenhariama/</t>
+          <t>https://www.ergus.com.br</t>
         </is>
       </c>
       <c r="X20" s="6" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y20" s="7" t="inlineStr">
         <is>
-          <t>Torre SUL do Giardino. 15 pav × 4 un = 60 unidades. 4 tipologias: 99,08 / 101,31 / 93,18 / 93,62 m². Tabela MAR/2026: 5 unidades disponíveis (701/101 col 99m², 1502/1402 col 101m², 104 col 93m²) = ~8% estoque, 92% VENDIDO → Últimas unidades. CORREÇÃO v5.1: dorms = 3 suítes (descrição da tabela MAR/26), antes constava '2 suítes/1 suíte' incorretamente. 2 vagas + 1 depósito. Mais acessível que Torre Fiore. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL.</t>
+          <t>2 torres, 2 aptos/andar, 15 andares. Elevadores triplos. Treinamento corretor 12/09/2025 confirma lançamento comercial ~set/2025.</t>
         </is>
       </c>
     </row>
     <row r="21" ht="52" customHeight="1">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Berg Engenharia</t>
         </is>
       </c>
       <c r="B21" s="12" t="inlineStr">
         <is>
-          <t>Vernazza Torre Norte</t>
+          <t>Mount Solaro</t>
         </is>
       </c>
       <c r="C21" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E21" s="12" t="inlineStr">
@@ -2364,106 +2330,88 @@
       </c>
       <c r="F21" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H21" s="12" t="n">
-        <v>120</v>
-      </c>
+          <t>Pré-lançamento</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="n"/>
       <c r="I21" s="12" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025 ⚠ T-36</t>
         </is>
       </c>
       <c r="J21" s="12" t="inlineStr">
         <is>
-          <t>12/2029</t>
-        </is>
-      </c>
-      <c r="K21" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="L21" s="14" t="n">
-        <v>130</v>
-      </c>
-      <c r="M21" s="14" t="n">
-        <v>130</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K21" s="14" t="n"/>
+      <c r="L21" s="14" t="n"/>
+      <c r="M21" s="14" t="n"/>
       <c r="N21" s="13" t="inlineStr">
         <is>
-          <t>Aptos 130 m² — Leste/Sul/Norte</t>
-        </is>
-      </c>
-      <c r="O21" s="15" t="n">
-        <v>1820000</v>
-      </c>
-      <c r="P21" s="15" t="n">
-        <v>2235000</v>
-      </c>
-      <c r="Q21" s="15" t="n">
-        <v>15596.15384615385</v>
-      </c>
-      <c r="R21" s="15" t="n">
-        <v>243300000</v>
-      </c>
-      <c r="S21" s="16" t="n">
-        <v>0.5333333333333333</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="15" t="n"/>
+      <c r="S21" s="16" t="n"/>
       <c r="T21" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U21" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V21" s="12" t="inlineStr">
         <is>
-          <t>informado</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W21" s="12" t="inlineStr">
         <is>
-          <t>https://www.treviso.com.br</t>
+          <t>https://www.bergengenharia.com.br</t>
         </is>
       </c>
       <c r="X21" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y21" s="13" t="inlineStr">
         <is>
-          <t>Lançamento 02/2025 informado pelo Rafael (fonte externa confiável). Tabela de 02/2026 arquivada confirma vendas ativas naquela data, mas não é data de lançamento — aguarda book ou memorial para data confiável. Torre Norte: 37 unid, área 130 m², ticket R$ 1,82-2,24M (méd R$ 2,02M). R$/m² méd R$ 15.524. VGV listado R$ 74,8M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>SPE Berg + Gonçalves requereu Licença de Instalação (Diário Oficial SL).</t>
         </is>
       </c>
     </row>
     <row r="22" ht="52" customHeight="1">
       <c r="A22" s="5" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Monteplan</t>
         </is>
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>Vernazza Torre Sul</t>
+          <t>Renaissance Conceito</t>
         </is>
       </c>
       <c r="C22" s="7" t="inlineStr">
         <is>
-          <t>Ponta d'Areia, São Luís - MA</t>
+          <t>Rua Caxuxa, S/N, Renascença II, São Luís - MA</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Renascença II</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
@@ -2478,85 +2426,73 @@
       </c>
       <c r="G22" s="6" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
+          <t>Lançamento</t>
         </is>
       </c>
       <c r="H22" s="6" t="n"/>
       <c r="I22" s="6" t="inlineStr">
         <is>
-          <t>02/2025</t>
+          <t>06/2025 ⚠ T-36</t>
         </is>
       </c>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>12/2029</t>
-        </is>
-      </c>
-      <c r="K22" s="8" t="n">
-        <v>87.98</v>
-      </c>
-      <c r="L22" s="8" t="n">
-        <v>90.09999999999999</v>
-      </c>
-      <c r="M22" s="8" t="n">
-        <v>89.03999999999999</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K22" s="8" t="n"/>
+      <c r="L22" s="8" t="n"/>
+      <c r="M22" s="8" t="n"/>
       <c r="N22" s="7" t="inlineStr">
         <is>
-          <t>87,98 e 90,10 m² (Norte/Sul)</t>
-        </is>
-      </c>
-      <c r="O22" s="9" t="n">
-        <v>1277000</v>
-      </c>
-      <c r="P22" s="9" t="n">
-        <v>1586000</v>
-      </c>
-      <c r="Q22" s="9" t="n">
-        <v>16077.04402515723</v>
-      </c>
+          <t>3Q</t>
+        </is>
+      </c>
+      <c r="O22" s="9" t="n"/>
+      <c r="P22" s="9" t="n"/>
+      <c r="Q22" s="9" t="n"/>
       <c r="R22" s="9" t="n"/>
       <c r="S22" s="10" t="n"/>
       <c r="T22" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U22" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V22" s="6" t="inlineStr">
         <is>
-          <t>informado</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W22" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>https://monteplanengenharia.com.br/empreendimentos/renaissance-conceito/</t>
         </is>
       </c>
       <c r="X22" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y22" s="7" t="inlineStr">
         <is>
-          <t>Lançamento 02/2025 informado pelo Rafael. 26 unid listadas, área 87,98/90,10 m². Ticket R$ 1,28-1,59M (méd R$ 1,40M). R$/m² pond R$ 15.600 (faixa R$ 14,2-17,6k). VGV listado R$ 36,3M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Alto padrão Renascença II (Loteamento Boa Vista). Dois torres, lazer completo.</t>
         </is>
       </c>
     </row>
     <row r="23" ht="52" customHeight="1">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t>Berg Engenharia</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B23" s="12" t="inlineStr">
         <is>
-          <t>Mount Solaro</t>
+          <t>Villagio Treviso</t>
         </is>
       </c>
       <c r="C23" s="13" t="inlineStr">
@@ -2571,7 +2507,7 @@
       </c>
       <c r="E23" s="12" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -2581,13 +2517,13 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Pré-lançamento</t>
+          <t>Em comercialização</t>
         </is>
       </c>
       <c r="H23" s="12" t="n"/>
       <c r="I23" s="12" t="inlineStr">
         <is>
-          <t>~2025</t>
+          <t>06/2025 ⚠ T-36</t>
         </is>
       </c>
       <c r="J23" s="12" t="inlineStr">
@@ -2600,7 +2536,7 @@
       <c r="M23" s="14" t="n"/>
       <c r="N23" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Terrenos em condomínio</t>
         </is>
       </c>
       <c r="O23" s="15" t="n"/>
@@ -2620,12 +2556,12 @@
       </c>
       <c r="V23" s="12" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W23" s="12" t="inlineStr">
         <is>
-          <t>https://www.bergengenharia.com.br</t>
+          <t>https://trevisoengenharia.com.br</t>
         </is>
       </c>
       <c r="X23" s="12" t="inlineStr">
@@ -2635,29 +2571,29 @@
       </c>
       <c r="Y23" s="13" t="inlineStr">
         <is>
-          <t>SPE Berg + Gonçalves requereu Licença de Instalação (Diário Oficial SL).</t>
+          <t>Condomínio de terrenos (loteamento fechado). Divulgação ativa abr/2026. Sem tabela pública mapeada.</t>
         </is>
       </c>
     </row>
     <row r="24" ht="52" customHeight="1">
       <c r="A24" s="5" t="inlineStr">
         <is>
-          <t>Monteplan</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>Renaissance Conceito</t>
+          <t>Studio Design 7 Península</t>
         </is>
       </c>
       <c r="C24" s="7" t="inlineStr">
         <is>
-          <t>Rua Caxuxa, S/N, Renascença II, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>Renascença II</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
@@ -2672,51 +2608,69 @@
       </c>
       <c r="G24" s="6" t="inlineStr">
         <is>
-          <t>Lançamento</t>
-        </is>
-      </c>
-      <c r="H24" s="6" t="n"/>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>125</v>
+      </c>
       <c r="I24" s="6" t="inlineStr">
         <is>
-          <t>~2025</t>
+          <t>04/2025 ⚠ T-36</t>
         </is>
       </c>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K24" s="8" t="n"/>
-      <c r="L24" s="8" t="n"/>
-      <c r="M24" s="8" t="n"/>
+          <t>04/2028</t>
+        </is>
+      </c>
+      <c r="K24" s="8" t="n">
+        <v>43</v>
+      </c>
+      <c r="L24" s="8" t="n">
+        <v>64</v>
+      </c>
+      <c r="M24" s="8" t="n">
+        <v>53.5</v>
+      </c>
       <c r="N24" s="7" t="inlineStr">
         <is>
-          <t>3Q</t>
-        </is>
-      </c>
-      <c r="O24" s="9" t="n"/>
-      <c r="P24" s="9" t="n"/>
-      <c r="Q24" s="9" t="n"/>
-      <c r="R24" s="9" t="n"/>
-      <c r="S24" s="10" t="n"/>
+          <t>Studio / 1Q</t>
+        </is>
+      </c>
+      <c r="O24" s="9" t="n">
+        <v>710000</v>
+      </c>
+      <c r="P24" s="9" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="Q24" s="9" t="n">
+        <v>15981.30841121495</v>
+      </c>
+      <c r="R24" s="9" t="n">
+        <v>106875000</v>
+      </c>
+      <c r="S24" s="10" t="n">
+        <v>0.736</v>
+      </c>
       <c r="T24" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U24" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V24" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>estimativa_T-36</t>
         </is>
       </c>
       <c r="W24" s="6" t="inlineStr">
         <is>
-          <t>https://monteplanengenharia.com.br/empreendimentos/renaissance-conceito/</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="X24" s="6" t="inlineStr">
@@ -2726,120 +2680,132 @@
       </c>
       <c r="Y24" s="7" t="inlineStr">
         <is>
-          <t>Alto padrão Renascença II (Loteamento Boa Vista). Dois torres, lazer completo.</t>
+          <t>33 de 125 aptos à venda. ≈74% vendido em ~18 meses. Forte velocidade em compactos.</t>
         </is>
       </c>
     </row>
     <row r="25" ht="52" customHeight="1">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Hiali</t>
         </is>
       </c>
       <c r="B25" s="12" t="inlineStr">
         <is>
-          <t>Villagio Treviso</t>
+          <t>Le Noir</t>
         </is>
       </c>
       <c r="C25" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>Rua Osires, 05, Renascença II, São Luís - MA</t>
         </is>
       </c>
       <c r="D25" s="12" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Renascença II</t>
         </is>
       </c>
       <c r="E25" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H25" s="12" t="n"/>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="H25" s="12" t="n">
+        <v>25</v>
+      </c>
       <c r="I25" s="12" t="inlineStr">
         <is>
-          <t>~2025</t>
+          <t>04/2025</t>
         </is>
       </c>
       <c r="J25" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K25" s="14" t="n"/>
-      <c r="L25" s="14" t="n"/>
-      <c r="M25" s="14" t="n"/>
+          <t>12/2027</t>
+        </is>
+      </c>
+      <c r="K25" s="14" t="n">
+        <v>49.74</v>
+      </c>
+      <c r="L25" s="14" t="n">
+        <v>62.62</v>
+      </c>
+      <c r="M25" s="14" t="n">
+        <v>56.18</v>
+      </c>
       <c r="N25" s="13" t="inlineStr">
         <is>
-          <t>Terrenos em condomínio</t>
-        </is>
-      </c>
-      <c r="O25" s="15" t="n"/>
-      <c r="P25" s="15" t="n"/>
-      <c r="Q25" s="15" t="n"/>
-      <c r="R25" s="15" t="n"/>
+          <t>Studios e 1-2 dorm (compactos premium)</t>
+        </is>
+      </c>
+      <c r="O25" s="15" t="n">
+        <v>710000</v>
+      </c>
+      <c r="P25" s="15" t="n">
+        <v>870000</v>
+      </c>
+      <c r="Q25" s="15" t="n">
+        <v>14061.94375222499</v>
+      </c>
+      <c r="R25" s="15" t="n">
+        <v>19750000</v>
+      </c>
       <c r="S25" s="16" t="n"/>
       <c r="T25" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U25" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="V25" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
-        </is>
-      </c>
-      <c r="W25" s="12" t="inlineStr">
-        <is>
-          <t>https://trevisoengenharia.com.br</t>
-        </is>
-      </c>
+          <t>memorial</t>
+        </is>
+      </c>
+      <c r="W25" s="12" t="inlineStr"/>
       <c r="X25" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y25" s="13" t="inlineStr">
         <is>
-          <t>Condomínio de terrenos (loteamento fechado). Divulgação ativa abr/2026. Sem tabela pública mapeada.</t>
+          <t>Parceria Hiali + Silveira Inc. Compactos premium: 49,74 / 58,91 / 62,62 m². 5 pavimentos tipo × 5 aptos/andar = ~25 unidades. Entrega DEZ/2027. Ticket R$ 710-870k. R$/m² méd R$ 13.810. Memorial R.09/25.101 registrado 17/04/2025 no 1º RI São Luís. Foco em mercado jovem / investidor. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="26" ht="52" customHeight="1">
       <c r="A26" s="5" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>Sky Residence</t>
+          <t>Giardino Residenza Torre Fiore</t>
         </is>
       </c>
       <c r="C26" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Ponta do Farol, São Luís - MA</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Ponta do Farol</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
@@ -2849,7 +2815,7 @@
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G26" s="6" t="inlineStr">
@@ -2858,46 +2824,46 @@
         </is>
       </c>
       <c r="H26" s="6" t="n">
-        <v>12</v>
+        <v>45</v>
       </c>
       <c r="I26" s="6" t="inlineStr">
         <is>
-          <t>09/2024 ⚠ T-36</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>09/2027</t>
+          <t>12/2029</t>
         </is>
       </c>
       <c r="K26" s="8" t="n">
-        <v>246.69</v>
+        <v>110.77</v>
       </c>
       <c r="L26" s="8" t="n">
-        <v>246.69</v>
+        <v>128.37</v>
       </c>
       <c r="M26" s="8" t="n">
-        <v>246.69</v>
+        <v>119.57</v>
       </c>
       <c r="N26" s="7" t="inlineStr">
         <is>
-          <t>4 suítes</t>
+          <t>2 suítes + 2 semi-suítes OU 3 suítes, varanda, lavabo, 3 vagas, depósito</t>
         </is>
       </c>
       <c r="O26" s="9" t="n">
-        <v>4700000</v>
+        <v>1838492</v>
       </c>
       <c r="P26" s="9" t="n">
-        <v>4700000</v>
+        <v>2032939</v>
       </c>
       <c r="Q26" s="9" t="n">
-        <v>19052.25181401759</v>
+        <v>16188.97298653509</v>
       </c>
       <c r="R26" s="9" t="n">
-        <v>56400000</v>
+        <v>87107197.5</v>
       </c>
       <c r="S26" s="10" t="n">
-        <v>0.9166666666666666</v>
+        <v>0.8666666666666667</v>
       </c>
       <c r="T26" s="6" t="inlineStr">
         <is>
@@ -2911,44 +2877,44 @@
       </c>
       <c r="V26" s="6" t="inlineStr">
         <is>
-          <t>estimativa_T-36</t>
+          <t>memorial</t>
         </is>
       </c>
       <c r="W26" s="6" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://www.instagram.com/alfaengenhariama/</t>
         </is>
       </c>
       <c r="X26" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="Y26" s="7" t="inlineStr">
         <is>
-          <t>Prédio pequeno (12 aptos). 1 à venda. ≈92% vendido.</t>
+          <t>Torre NORTE do Giardino. 15 pav × 3 un = 45 unidades. 3 tipologias: 127,30 / 128,37 / 110,77 m². Tabela MAR/2026: 6 unidades disponíveis (1001/701/201/101 da coluna 127m², 102 da coluna 128m², 1403 da coluna 110m²) = ~13% estoque, 87% VENDIDO → Últimas unidades. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL. Endereço Alfa: Rua Peixe Pedra, Qd 12 lote 04, Calhau.</t>
         </is>
       </c>
     </row>
     <row r="27" ht="52" customHeight="1">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t>Mota Machado</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B27" s="12" t="inlineStr">
         <is>
-          <t>Al Mare Tirreno</t>
+          <t>Giardino Residenza Torre Luce</t>
         </is>
       </c>
       <c r="C27" s="13" t="inlineStr">
         <is>
-          <t>Av. dos Holandeses, Qd 9 Lt 9, São Marcos, São Luís - MA</t>
+          <t>Ponta do Farol, São Luís - MA</t>
         </is>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
-          <t>São Marcos</t>
+          <t>Ponta do Farol</t>
         </is>
       </c>
       <c r="E27" s="12" t="inlineStr">
@@ -2963,95 +2929,101 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H27" s="12" t="n"/>
+          <t>Últimas unidades</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="n">
+        <v>60</v>
+      </c>
       <c r="I27" s="12" t="inlineStr">
         <is>
-          <t>08/2024</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="J27" s="12" t="inlineStr">
         <is>
-          <t>Pronto</t>
+          <t>12/2029</t>
         </is>
       </c>
       <c r="K27" s="14" t="n">
-        <v>215</v>
+        <v>93.18000000000001</v>
       </c>
       <c r="L27" s="14" t="n">
-        <v>215</v>
+        <v>101.31</v>
       </c>
       <c r="M27" s="14" t="n">
-        <v>215</v>
+        <v>97.245</v>
       </c>
       <c r="N27" s="13" t="inlineStr">
         <is>
-          <t>4 suítes, 3 vagas</t>
+          <t>3 suítes, varanda, lavabo, 2 vagas, depósito</t>
         </is>
       </c>
       <c r="O27" s="15" t="n">
-        <v>3025856</v>
+        <v>1442168</v>
       </c>
       <c r="P27" s="15" t="n">
-        <v>3120721</v>
+        <v>1595303</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <v>14294.36511627907</v>
-      </c>
-      <c r="R27" s="15" t="n"/>
-      <c r="S27" s="16" t="n"/>
+        <v>15617.62044321045</v>
+      </c>
+      <c r="R27" s="15" t="n">
+        <v>91124130</v>
+      </c>
+      <c r="S27" s="16" t="n">
+        <v>0.9166666666666666</v>
+      </c>
       <c r="T27" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U27" s="12" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V27" s="12" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>memorial</t>
         </is>
       </c>
       <c r="W27" s="12" t="inlineStr">
         <is>
-          <t>https://motamachado.com.br</t>
+          <t>https://www.instagram.com/alfaengenhariama/</t>
         </is>
       </c>
       <c r="X27" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="Y27" s="13" t="inlineStr">
         <is>
-          <t>Torre A 'Tirreno' da Mota Machado Collection. Imóvel PRONTO. 215 m², 4 suítes, 3 vagas. Apts 102, 201, 202 listados. Ticket R$ 3,02-3,12M. R$/m² méd R$ 14.293. Av. dos Holandeses / São Marcos. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Torre SUL do Giardino. 15 pav × 4 un = 60 unidades. 4 tipologias: 99,08 / 101,31 / 93,18 / 93,62 m². Tabela MAR/2026: 5 unidades disponíveis (701/101 col 99m², 1502/1402 col 101m², 104 col 93m²) = ~8% estoque, 92% VENDIDO → Últimas unidades. CORREÇÃO v5.1: dorms = 3 suítes (descrição da tabela MAR/26), antes constava '2 suítes/1 suíte' incorretamente. 2 vagas + 1 depósito. Mais acessível que Torre Fiore. Entrega DEZ/29. Memorial R.06/56.931 - 1º RI SL.</t>
         </is>
       </c>
     </row>
     <row r="28" ht="52" customHeight="1">
       <c r="A28" s="5" t="inlineStr">
         <is>
-          <t>Mota Machado</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>Entre Rios</t>
+          <t>Vernazza Torre Norte</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
         <is>
-          <t>Rua dos Bicudos, S/N, Qd. XIV-A Lote 02, Renascença, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>Renascença</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
@@ -3066,63 +3038,69 @@
       </c>
       <c r="G28" s="6" t="inlineStr">
         <is>
-          <t>Lançamento</t>
-        </is>
-      </c>
-      <c r="H28" s="6" t="n"/>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>120</v>
+      </c>
       <c r="I28" s="6" t="inlineStr">
         <is>
-          <t>08/2024</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12/2029</t>
         </is>
       </c>
       <c r="K28" s="8" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="L28" s="8" t="n">
-        <v>157</v>
+        <v>130</v>
       </c>
       <c r="M28" s="8" t="n">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="N28" s="7" t="inlineStr">
         <is>
-          <t>3 suítes (1 master)</t>
+          <t>Aptos 130 m² — Leste/Sul/Norte</t>
         </is>
       </c>
       <c r="O28" s="9" t="n">
-        <v>1732000</v>
+        <v>1820000</v>
       </c>
       <c r="P28" s="9" t="n">
-        <v>2720000</v>
+        <v>2235000</v>
       </c>
       <c r="Q28" s="9" t="n">
-        <v>15787.23404255319</v>
-      </c>
-      <c r="R28" s="9" t="n"/>
-      <c r="S28" s="10" t="n"/>
+        <v>15596.15384615385</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>243300000</v>
+      </c>
+      <c r="S28" s="10" t="n">
+        <v>0.5333333333333333</v>
+      </c>
       <c r="T28" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U28" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V28" s="6" t="inlineStr">
         <is>
-          <t>book</t>
+          <t>informado</t>
         </is>
       </c>
       <c r="W28" s="6" t="inlineStr">
         <is>
-          <t>https://motamachado.com.br</t>
+          <t>https://www.treviso.com.br</t>
         </is>
       </c>
       <c r="X28" s="6" t="inlineStr">
@@ -3132,39 +3110,39 @@
       </c>
       <c r="Y28" s="7" t="inlineStr">
         <is>
-          <t>3 tipologias (125 / 146,82 / 156,94 m²). 2 torres x 15 pav. Tab ABR/26: 15 unid, VGV R$ 32,3M. Ticket R$ 1,73–2,72M (méd R$ 2,15M). R$/m² pond R$ 15.162 (faixa R$ 13,9k–17,3k). Rua dos Bicudos, Renascença. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Lançamento 02/2025 informado pelo Rafael (fonte externa confiável). Tabela de 02/2026 arquivada confirma vendas ativas naquela data, mas não é data de lançamento — aguarda book ou memorial para data confiável. Torre Norte: 37 unid, área 130 m², ticket R$ 1,82-2,24M (méd R$ 2,02M). R$/m² méd R$ 15.524. VGV listado R$ 74,8M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="29" ht="52" customHeight="1">
       <c r="A29" s="11" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B29" s="12" t="inlineStr">
         <is>
-          <t>Dom José</t>
+          <t>Vernazza Torre Sul</t>
         </is>
       </c>
       <c r="C29" s="13" t="inlineStr">
         <is>
-          <t>FQV9+JJ Jardim Eldorado, São Luís - MA</t>
+          <t>Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
-          <t>Jardim Eldorado</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E29" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -3175,36 +3153,36 @@
       <c r="H29" s="12" t="n"/>
       <c r="I29" s="12" t="inlineStr">
         <is>
-          <t>06/2024</t>
+          <t>02/2025</t>
         </is>
       </c>
       <c r="J29" s="12" t="inlineStr">
         <is>
-          <t>06/2027</t>
+          <t>12/2029</t>
         </is>
       </c>
       <c r="K29" s="14" t="n">
-        <v>154.64</v>
+        <v>87.98</v>
       </c>
       <c r="L29" s="14" t="n">
-        <v>180.98</v>
+        <v>90.09999999999999</v>
       </c>
       <c r="M29" s="14" t="n">
-        <v>167.81</v>
+        <v>89.03999999999999</v>
       </c>
       <c r="N29" s="13" t="inlineStr">
         <is>
-          <t>Casa 4+ dorm, alto padrão</t>
+          <t>87,98 e 90,10 m² (Norte/Sul)</t>
         </is>
       </c>
       <c r="O29" s="15" t="n">
-        <v>1400000</v>
+        <v>1277000</v>
       </c>
       <c r="P29" s="15" t="n">
-        <v>1415000</v>
+        <v>1586000</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <v>8387.462010607234</v>
+        <v>16077.04402515723</v>
       </c>
       <c r="R29" s="15" t="n"/>
       <c r="S29" s="16" t="n"/>
@@ -3220,10 +3198,14 @@
       </c>
       <c r="V29" s="12" t="inlineStr">
         <is>
-          <t>interno</t>
-        </is>
-      </c>
-      <c r="W29" s="12" t="inlineStr"/>
+          <t>informado</t>
+        </is>
+      </c>
+      <c r="W29" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="X29" s="12" t="inlineStr">
         <is>
           <t>23/04/2026</t>
@@ -3231,29 +3213,29 @@
       </c>
       <c r="Y29" s="13" t="inlineStr">
         <is>
-          <t>Condomínio horizontal alto padrão. Casa 154,64 m² + terreno 170-181 m². Maioria das unidades VENDIDAS (14+ marcadas VENDIDA na tabela ABR/2026). Entrega JUL/2027. Ticket ~R$ 1,4M. R$/m² construção ~R$ 9.150. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Lançamento 02/2025 informado pelo Rafael. 26 unid listadas, área 87,98/90,10 m². Ticket R$ 1,28-1,59M (méd R$ 1,40M). R$/m² pond R$ 15.600 (faixa R$ 14,2-17,6k). VGV listado R$ 36,3M. Entrega 12/2029. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="30" ht="52" customHeight="1">
       <c r="A30" s="5" t="inlineStr">
         <is>
-          <t>Berg Engenharia</t>
+          <t>Mota Machado</t>
         </is>
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>Monte Meru</t>
+          <t>Reserva São Marcos</t>
         </is>
       </c>
       <c r="C30" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Endereço não localizado, Calhau, São Luís - MA</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>Calhau</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
@@ -3274,79 +3256,67 @@
       <c r="H30" s="6" t="n"/>
       <c r="I30" s="6" t="inlineStr">
         <is>
-          <t>04/2024</t>
+          <t>01/2025</t>
         </is>
       </c>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>04/2027</t>
-        </is>
-      </c>
-      <c r="K30" s="8" t="n">
-        <v>135.32</v>
-      </c>
-      <c r="L30" s="8" t="n">
-        <v>135.83</v>
-      </c>
-      <c r="M30" s="8" t="n">
-        <v>135.575</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K30" s="8" t="n"/>
+      <c r="L30" s="8" t="n"/>
+      <c r="M30" s="8" t="n"/>
       <c r="N30" s="7" t="inlineStr">
         <is>
-          <t>Aptos 135 m², 2-3 vagas</t>
-        </is>
-      </c>
-      <c r="O30" s="9" t="n">
-        <v>1932400</v>
-      </c>
-      <c r="P30" s="9" t="n">
-        <v>1944500</v>
-      </c>
-      <c r="Q30" s="9" t="n">
-        <v>14297.99004241195</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O30" s="9" t="n"/>
+      <c r="P30" s="9" t="n"/>
+      <c r="Q30" s="9" t="n"/>
       <c r="R30" s="9" t="n"/>
       <c r="S30" s="10" t="n"/>
       <c r="T30" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U30" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V30" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W30" s="6" t="inlineStr">
         <is>
-          <t>https://www.bergengenharia.com.br</t>
+          <t>https://www.motamachado.com.br</t>
         </is>
       </c>
       <c r="X30" s="6" t="inlineStr">
         <is>
-          <t>27/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y30" s="7" t="inlineStr">
         <is>
-          <t>Tabela ABR/2026 (Berg Engenharia). 4 tipologias (1-4) com áreas similares 135,32 / 135,83 m². Lançamento 04/2024 estimado pela pasta. Conclusão: 30/04/2027 (T-36 perfeito). Tipo 3 (135,32m²): apto 103 disponível R$ 1.932.400. Tipo 4 (135,83m²): apto 104 disponível R$ 1.944.500, demais (204-1004) VENDIDOS = 9 vendidos no Tipo 4 → estoque concentrado em 1 unidade visível. Apto 704 tem 3 vagas (diferencial). Correção INCC. Histórico Berg: Montparnasse, Golden Tower, Peninsula Mall, Monte Olimpo, Monte Fuji.</t>
+          <t>Obras iniciadas 09/2025. Empresa de Fortaleza expandindo no Nordeste. SEM material local.</t>
         </is>
       </c>
     </row>
     <row r="31" ht="52" customHeight="1">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B31" s="12" t="inlineStr">
         <is>
-          <t>Connect Península</t>
+          <t>Sky Residence</t>
         </is>
       </c>
       <c r="C31" s="13" t="inlineStr">
@@ -3366,56 +3336,74 @@
       </c>
       <c r="F31" s="12" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Pré-lançamento</t>
-        </is>
-      </c>
-      <c r="H31" s="12" t="n"/>
+          <t>Últimas unidades</t>
+        </is>
+      </c>
+      <c r="H31" s="12" t="n">
+        <v>12</v>
+      </c>
       <c r="I31" s="12" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>09/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="J31" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K31" s="14" t="n"/>
-      <c r="L31" s="14" t="n"/>
-      <c r="M31" s="14" t="n"/>
+          <t>09/2027</t>
+        </is>
+      </c>
+      <c r="K31" s="14" t="n">
+        <v>246.69</v>
+      </c>
+      <c r="L31" s="14" t="n">
+        <v>246.69</v>
+      </c>
+      <c r="M31" s="14" t="n">
+        <v>246.69</v>
+      </c>
       <c r="N31" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O31" s="15" t="n"/>
-      <c r="P31" s="15" t="n"/>
-      <c r="Q31" s="15" t="n"/>
-      <c r="R31" s="15" t="n"/>
-      <c r="S31" s="16" t="n"/>
+          <t>4 suítes</t>
+        </is>
+      </c>
+      <c r="O31" s="15" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="P31" s="15" t="n">
+        <v>4700000</v>
+      </c>
+      <c r="Q31" s="15" t="n">
+        <v>19052.25181401759</v>
+      </c>
+      <c r="R31" s="15" t="n">
+        <v>56400000</v>
+      </c>
+      <c r="S31" s="16" t="n">
+        <v>0.9166666666666666</v>
+      </c>
       <c r="T31" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U31" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V31" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>estimativa_T-36</t>
         </is>
       </c>
       <c r="W31" s="12" t="inlineStr">
         <is>
-          <t>https://www.alfaengenharia.com.br</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="X31" s="12" t="inlineStr">
@@ -3425,29 +3413,29 @@
       </c>
       <c r="Y31" s="13" t="inlineStr">
         <is>
-          <t>Tipologia a confirmar em book/site/Instagram. Tecnologia Housi (gestão de locação) NÃO determina tipologia — descrição anterior corrigida. Sem tabela comercial pública.</t>
+          <t>Prédio pequeno (12 aptos). 1 à venda. ≈92% vendido.</t>
         </is>
       </c>
     </row>
     <row r="32" ht="52" customHeight="1">
       <c r="A32" s="5" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Mota Machado</t>
         </is>
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>LIV Residence</t>
+          <t>Al Mare Tirreno</t>
         </is>
       </c>
       <c r="C32" s="7" t="inlineStr">
         <is>
-          <t>Rua Aziz Heluy, S/N, Ponta d'Areia, São Luís - MA</t>
+          <t>Av. dos Holandeses, Qd 9 Lt 9, São Marcos, São Luís - MA</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Marcos</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
@@ -3462,104 +3450,116 @@
       </c>
       <c r="G32" s="6" t="inlineStr">
         <is>
-          <t>Lançamento</t>
+          <t>Em comercialização</t>
         </is>
       </c>
       <c r="H32" s="6" t="n"/>
       <c r="I32" s="6" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>08/2024</t>
         </is>
       </c>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K32" s="8" t="n"/>
-      <c r="L32" s="8" t="n"/>
-      <c r="M32" s="8" t="n"/>
+          <t>Pronto</t>
+        </is>
+      </c>
+      <c r="K32" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="L32" s="8" t="n">
+        <v>215</v>
+      </c>
+      <c r="M32" s="8" t="n">
+        <v>215</v>
+      </c>
       <c r="N32" s="7" t="inlineStr">
         <is>
-          <t>3 suítes</t>
-        </is>
-      </c>
-      <c r="O32" s="9" t="n"/>
-      <c r="P32" s="9" t="n"/>
-      <c r="Q32" s="9" t="n"/>
+          <t>4 suítes, 3 vagas</t>
+        </is>
+      </c>
+      <c r="O32" s="9" t="n">
+        <v>3025856</v>
+      </c>
+      <c r="P32" s="9" t="n">
+        <v>3120721</v>
+      </c>
+      <c r="Q32" s="9" t="n">
+        <v>14294.36511627907</v>
+      </c>
       <c r="R32" s="9" t="n"/>
       <c r="S32" s="10" t="n"/>
       <c r="T32" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U32" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="V32" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>book</t>
         </is>
       </c>
       <c r="W32" s="6" t="inlineStr">
         <is>
-          <t>https://www.alfaengenharia.com.br</t>
+          <t>https://motamachado.com.br</t>
         </is>
       </c>
       <c r="X32" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y32" s="7" t="inlineStr">
         <is>
-          <t>1º Housi do MA. Book local + site Alfa. Sem tabela comercial.</t>
+          <t>Torre A 'Tirreno' da Mota Machado Collection. Imóvel PRONTO. 215 m², 4 suítes, 3 vagas. Apts 102, 201, 202 listados. Ticket R$ 3,02-3,12M. R$/m² méd R$ 14.293. Av. dos Holandeses / São Marcos. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="33" ht="52" customHeight="1">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t>Castelucci</t>
+          <t>Mota Machado</t>
         </is>
       </c>
       <c r="B33" s="12" t="inlineStr">
         <is>
-          <t>Villa di Carpi</t>
+          <t>Entre Rios</t>
         </is>
       </c>
       <c r="C33" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Cohatrac, São Luís - MA</t>
+          <t>Rua dos Bicudos, S/N, Qd. XIV-A Lote 02, Renascença, São Luís - MA</t>
         </is>
       </c>
       <c r="D33" s="12" t="inlineStr">
         <is>
-          <t>Cohatrac</t>
+          <t>Renascença</t>
         </is>
       </c>
       <c r="E33" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
+          <t>Lançamento</t>
         </is>
       </c>
       <c r="H33" s="12" t="n"/>
       <c r="I33" s="12" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>08/2024</t>
         </is>
       </c>
       <c r="J33" s="12" t="inlineStr">
@@ -3568,74 +3568,80 @@
         </is>
       </c>
       <c r="K33" s="14" t="n">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="L33" s="14" t="n">
-        <v>52</v>
+        <v>157</v>
       </c>
       <c r="M33" s="14" t="n">
-        <v>50.5</v>
+        <v>141</v>
       </c>
       <c r="N33" s="13" t="inlineStr">
         <is>
-          <t>2Q</t>
-        </is>
-      </c>
-      <c r="O33" s="15" t="n"/>
-      <c r="P33" s="15" t="n"/>
-      <c r="Q33" s="15" t="n"/>
+          <t>3 suítes (1 master)</t>
+        </is>
+      </c>
+      <c r="O33" s="15" t="n">
+        <v>1732000</v>
+      </c>
+      <c r="P33" s="15" t="n">
+        <v>2720000</v>
+      </c>
+      <c r="Q33" s="15" t="n">
+        <v>15787.23404255319</v>
+      </c>
       <c r="R33" s="15" t="n"/>
       <c r="S33" s="16" t="n"/>
       <c r="T33" s="12" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U33" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="V33" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>book</t>
         </is>
       </c>
       <c r="W33" s="12" t="inlineStr">
         <is>
-          <t>https://construtoracastelucci.com.br</t>
+          <t>https://motamachado.com.br</t>
         </is>
       </c>
       <c r="X33" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y33" s="13" t="inlineStr">
         <is>
-          <t>Compactos 49-52m², 2Q. Público Cohatrac/médio. Instagram @construtoracastelucci anunciou como lançamento; preço não divulgado.</t>
+          <t>3 tipologias (125 / 146,82 / 156,94 m²). 2 torres x 15 pav. Tab ABR/26: 15 unid, VGV R$ 32,3M. Ticket R$ 1,73–2,72M (méd R$ 2,15M). R$/m² pond R$ 15.162 (faixa R$ 13,9k–17,3k). Rua dos Bicudos, Renascença. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="34" ht="52" customHeight="1">
       <c r="A34" s="5" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>Wave Residence</t>
+          <t>Connect Península</t>
         </is>
       </c>
       <c r="C34" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta do Farol, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>Ponta do Farol</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
@@ -3645,74 +3651,56 @@
       </c>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G34" s="6" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>30</v>
-      </c>
+          <t>Pré-lançamento</t>
+        </is>
+      </c>
+      <c r="H34" s="6" t="n"/>
       <c r="I34" s="6" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>07/2024</t>
         </is>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>03/2029</t>
-        </is>
-      </c>
-      <c r="K34" s="8" t="n">
-        <v>293.69</v>
-      </c>
-      <c r="L34" s="8" t="n">
-        <v>293.69</v>
-      </c>
-      <c r="M34" s="8" t="n">
-        <v>293.69</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K34" s="8" t="n"/>
+      <c r="L34" s="8" t="n"/>
+      <c r="M34" s="8" t="n"/>
       <c r="N34" s="7" t="inlineStr">
         <is>
-          <t>4 suítes</t>
-        </is>
-      </c>
-      <c r="O34" s="9" t="n">
-        <v>5500000</v>
-      </c>
-      <c r="P34" s="9" t="n">
-        <v>5800000</v>
-      </c>
-      <c r="Q34" s="9" t="n">
-        <v>19237.97201130444</v>
-      </c>
-      <c r="R34" s="9" t="n">
-        <v>169500000</v>
-      </c>
-      <c r="S34" s="10" t="n">
-        <v>0.8333333333333334</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="O34" s="9" t="n"/>
+      <c r="P34" s="9" t="n"/>
+      <c r="Q34" s="9" t="n"/>
+      <c r="R34" s="9" t="n"/>
+      <c r="S34" s="10" t="n"/>
       <c r="T34" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U34" s="6" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V34" s="6" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W34" s="6" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://www.alfaengenharia.com.br</t>
         </is>
       </c>
       <c r="X34" s="6" t="inlineStr">
@@ -3722,55 +3710,55 @@
       </c>
       <c r="Y34" s="7" t="inlineStr">
         <is>
-          <t>Evento de apresentação oficial 2024. 5 de 30 à venda. ≈83% vendido. Piscina privativa na varanda.</t>
+          <t>Tipologia a confirmar em book/site/Instagram. Tecnologia Housi (gestão de locação) NÃO determina tipologia — descrição anterior corrigida. Sem tabela comercial pública.</t>
         </is>
       </c>
     </row>
     <row r="35" ht="52" customHeight="1">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t>Franere</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B35" s="12" t="inlineStr">
         <is>
-          <t>Varandas Grand Park</t>
+          <t>Legacy Residence</t>
         </is>
       </c>
       <c r="C35" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D35" s="12" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E35" s="12" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
+          <t>Lançamento</t>
         </is>
       </c>
       <c r="H35" s="12" t="n"/>
       <c r="I35" s="12" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>07/2024</t>
         </is>
       </c>
       <c r="J35" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/2027</t>
         </is>
       </c>
       <c r="K35" s="14" t="n"/>
@@ -3778,7 +3766,7 @@
       <c r="M35" s="14" t="n"/>
       <c r="N35" s="13" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 suítes</t>
         </is>
       </c>
       <c r="O35" s="15" t="n"/>
@@ -3788,7 +3776,7 @@
       <c r="S35" s="16" t="n"/>
       <c r="T35" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U35" s="12" t="inlineStr">
@@ -3798,12 +3786,12 @@
       </c>
       <c r="V35" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W35" s="12" t="inlineStr">
         <is>
-          <t>https://franere.com.br</t>
+          <t>https://www.alfaengenharia.com.br</t>
         </is>
       </c>
       <c r="X35" s="12" t="inlineStr">
@@ -3813,34 +3801,34 @@
       </c>
       <c r="Y35" s="13" t="inlineStr">
         <is>
-          <t>Franere ('Maior construtora do Maranhão', 40 anos). Série 'Gran Park' tem múltiplos módulos. IG @franereoficial_.</t>
+          <t>13 opções de lazer, elevador privativo. Book local (375MB) + site oficial. Sem ticket público.</t>
         </is>
       </c>
     </row>
     <row r="36" ht="52" customHeight="1">
       <c r="A36" s="5" t="inlineStr">
         <is>
-          <t>Lua Nova</t>
+          <t>Castelucci</t>
         </is>
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>Lagoon Residence</t>
+          <t>Villa di Carpi</t>
         </is>
       </c>
       <c r="C36" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Santo Amaro, São Luís - MA</t>
+          <t>Endereço não localizado, Cohatrac, São Luís - MA</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>Santo Amaro</t>
+          <t>Cohatrac</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F36" s="6" t="inlineStr">
@@ -3856,7 +3844,7 @@
       <c r="H36" s="6" t="n"/>
       <c r="I36" s="6" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>06/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="J36" s="6" t="inlineStr">
@@ -3864,12 +3852,18 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K36" s="8" t="n"/>
-      <c r="L36" s="8" t="n"/>
-      <c r="M36" s="8" t="n"/>
+      <c r="K36" s="8" t="n">
+        <v>49</v>
+      </c>
+      <c r="L36" s="8" t="n">
+        <v>52</v>
+      </c>
+      <c r="M36" s="8" t="n">
+        <v>50.5</v>
+      </c>
       <c r="N36" s="7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2Q</t>
         </is>
       </c>
       <c r="O36" s="9" t="n"/>
@@ -3879,22 +3873,22 @@
       <c r="S36" s="10" t="n"/>
       <c r="T36" s="6" t="inlineStr">
         <is>
+          <t>agregador</t>
+        </is>
+      </c>
+      <c r="U36" s="6" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="V36" s="6" t="inlineStr">
+        <is>
           <t>site_oficial</t>
         </is>
       </c>
-      <c r="U36" s="6" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="V36" s="6" t="inlineStr">
-        <is>
-          <t>site_oficial</t>
-        </is>
-      </c>
       <c r="W36" s="6" t="inlineStr">
         <is>
-          <t>https://construtoraluanova.com.br</t>
+          <t>https://construtoracastelucci.com.br</t>
         </is>
       </c>
       <c r="X36" s="6" t="inlineStr">
@@ -3904,29 +3898,29 @@
       </c>
       <c r="Y36" s="7" t="inlineStr">
         <is>
-          <t>Residência no Santo Amaro — região com oferta crescente de médio padrão.</t>
+          <t>Compactos 49-52m², 2Q. Público Cohatrac/médio. Instagram @construtoracastelucci anunciou como lançamento; preço não divulgado.</t>
         </is>
       </c>
     </row>
     <row r="37" ht="52" customHeight="1">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Lua Nova</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B37" s="12" t="inlineStr">
         <is>
-          <t>Villa Adagio</t>
+          <t>Dom José</t>
         </is>
       </c>
       <c r="C37" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, São Luís - MA</t>
+          <t>FQV9+JJ Jardim Eldorado, São Luís - MA</t>
         </is>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
-          <t>São Luís</t>
+          <t>Jardim Eldorado</t>
         </is>
       </c>
       <c r="E37" s="12" t="inlineStr">
@@ -3936,7 +3930,7 @@
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Médio-alto</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -3947,87 +3941,95 @@
       <c r="H37" s="12" t="n"/>
       <c r="I37" s="12" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>06/2024</t>
         </is>
       </c>
       <c r="J37" s="12" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="K37" s="14" t="n"/>
-      <c r="L37" s="14" t="n"/>
-      <c r="M37" s="14" t="n"/>
+          <t>06/2027</t>
+        </is>
+      </c>
+      <c r="K37" s="14" t="n">
+        <v>154.64</v>
+      </c>
+      <c r="L37" s="14" t="n">
+        <v>180.98</v>
+      </c>
+      <c r="M37" s="14" t="n">
+        <v>167.81</v>
+      </c>
       <c r="N37" s="13" t="inlineStr">
         <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="O37" s="15" t="n"/>
-      <c r="P37" s="15" t="n"/>
-      <c r="Q37" s="15" t="n"/>
+          <t>Casa 4+ dorm, alto padrão</t>
+        </is>
+      </c>
+      <c r="O37" s="15" t="n">
+        <v>1400000</v>
+      </c>
+      <c r="P37" s="15" t="n">
+        <v>1415000</v>
+      </c>
+      <c r="Q37" s="15" t="n">
+        <v>8387.462010607234</v>
+      </c>
       <c r="R37" s="15" t="n"/>
       <c r="S37" s="16" t="n"/>
       <c r="T37" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U37" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="V37" s="12" t="inlineStr">
         <is>
-          <t>site_oficial</t>
-        </is>
-      </c>
-      <c r="W37" s="12" t="inlineStr">
-        <is>
-          <t>https://construtoraluanova.com.br</t>
-        </is>
-      </c>
+          <t>interno</t>
+        </is>
+      </c>
+      <c r="W37" s="12" t="inlineStr"/>
       <c r="X37" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y37" s="13" t="inlineStr">
         <is>
-          <t>Construtora Lua Nova desde 1985. IG @construtoraluanova. Detalhes tipologia/ticket a coletar via book.</t>
+          <t>Condomínio horizontal alto padrão. Casa 154,64 m² + terreno 170-181 m². Maioria das unidades VENDIDAS (14+ marcadas VENDIDA na tabela ABR/2026). Entrega JUL/2027. Ticket ~R$ 1,4M. R$/m² construção ~R$ 9.150. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="38" ht="52" customHeight="1">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>Mota Machado</t>
+          <t>Franere</t>
         </is>
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>Reserva São Marcos</t>
+          <t>Varandas Grand Park</t>
         </is>
       </c>
       <c r="C38" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Calhau, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>Calhau</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>Alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G38" s="6" t="inlineStr">
@@ -4038,7 +4040,7 @@
       <c r="H38" s="6" t="n"/>
       <c r="I38" s="6" t="inlineStr">
         <is>
-          <t>~2024</t>
+          <t>06/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="J38" s="6" t="inlineStr">
@@ -4076,7 +4078,7 @@
       </c>
       <c r="W38" s="6" t="inlineStr">
         <is>
-          <t>https://www.motamachado.com.br</t>
+          <t>https://franere.com.br</t>
         </is>
       </c>
       <c r="X38" s="6" t="inlineStr">
@@ -4086,34 +4088,34 @@
       </c>
       <c r="Y38" s="7" t="inlineStr">
         <is>
-          <t>Obras iniciadas 09/2025. Empresa de Fortaleza expandindo no Nordeste. SEM material local.</t>
+          <t>Franere ('Maior construtora do Maranhão', 40 anos). Série 'Gran Park' tem múltiplos módulos. IG @franereoficial_.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="52" customHeight="1">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Lua Nova</t>
         </is>
       </c>
       <c r="B39" s="12" t="inlineStr">
         <is>
-          <t>Edifício Dom Ricardo</t>
+          <t>Villa Adagio</t>
         </is>
       </c>
       <c r="C39" s="13" t="inlineStr">
         <is>
-          <t>Rua dos Rouxinóis, 8, Jardim Renascença, São Luís - MA</t>
+          <t>Endereço não localizado, São Luís - MA</t>
         </is>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
-          <t>Jardim Renascença</t>
+          <t>São Luís</t>
         </is>
       </c>
       <c r="E39" s="12" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -4123,13 +4125,13 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Últimas unidades</t>
+          <t>Em comercialização</t>
         </is>
       </c>
       <c r="H39" s="12" t="n"/>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>12/2023</t>
+          <t>06/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
@@ -4137,87 +4139,79 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K39" s="14" t="n">
-        <v>71</v>
-      </c>
-      <c r="L39" s="14" t="n">
-        <v>85</v>
-      </c>
-      <c r="M39" s="14" t="n">
-        <v>78</v>
-      </c>
+      <c r="K39" s="14" t="n"/>
+      <c r="L39" s="14" t="n"/>
+      <c r="M39" s="14" t="n"/>
       <c r="N39" s="13" t="inlineStr">
         <is>
-          <t>2-3Q</t>
+          <t>—</t>
         </is>
       </c>
       <c r="O39" s="15" t="n"/>
       <c r="P39" s="15" t="n"/>
       <c r="Q39" s="15" t="n"/>
       <c r="R39" s="15" t="n"/>
-      <c r="S39" s="16" t="n">
-        <v>0.9399999999999999</v>
-      </c>
+      <c r="S39" s="16" t="n"/>
       <c r="T39" s="12" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U39" s="12" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V39" s="12" t="inlineStr">
         <is>
-          <t>interno</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W39" s="12" t="inlineStr">
         <is>
-          <t>https://www.imeu.com.br/empreendimento/dom-ricardo-apartamentos-sao-luis-2-a-3-quartos-71-a-85-m/19044585-MIM</t>
+          <t>https://construtoraluanova.com.br</t>
         </is>
       </c>
       <c r="X39" s="12" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y39" s="13" t="inlineStr">
         <is>
-          <t>DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 12/2023 confirmado internamente. Próximo à Praça da Lagoa (Foguete). 'Sucesso de vendas, 6 unidades disponíveis' (IG jan/2025). Estoque estimado ≤6%. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Construtora Lua Nova desde 1985. IG @construtoraluanova. Detalhes tipologia/ticket a coletar via book.</t>
         </is>
       </c>
     </row>
     <row r="40" ht="52" customHeight="1">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>DOM Incorporação</t>
+          <t>Berg Engenharia</t>
         </is>
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>Dom Antônio</t>
+          <t>Monte Meru</t>
         </is>
       </c>
       <c r="C40" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Jardim Eldorado (Turú), São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>Jardim Eldorado</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>Médio</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G40" s="6" t="inlineStr">
@@ -4228,89 +4222,89 @@
       <c r="H40" s="6" t="n"/>
       <c r="I40" s="6" t="inlineStr">
         <is>
-          <t>06/2023</t>
+          <t>04/2024</t>
         </is>
       </c>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>04/2027</t>
         </is>
       </c>
       <c r="K40" s="8" t="n">
-        <v>136</v>
+        <v>135.32</v>
       </c>
       <c r="L40" s="8" t="n">
-        <v>136</v>
+        <v>135.83</v>
       </c>
       <c r="M40" s="8" t="n">
-        <v>136</v>
+        <v>135.575</v>
       </c>
       <c r="N40" s="7" t="inlineStr">
         <is>
-          <t>3Q casas duplex</t>
+          <t>Aptos 135 m², 2-3 vagas</t>
         </is>
       </c>
       <c r="O40" s="9" t="n">
-        <v>906870</v>
+        <v>1932400</v>
       </c>
       <c r="P40" s="9" t="n">
-        <v>906870</v>
+        <v>1944500</v>
       </c>
       <c r="Q40" s="9" t="n">
-        <v>6668.161764705882</v>
+        <v>14297.99004241195</v>
       </c>
       <c r="R40" s="9" t="n"/>
       <c r="S40" s="10" t="n"/>
       <c r="T40" s="6" t="inlineStr">
         <is>
-          <t>agregador</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U40" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V40" s="6" t="inlineStr">
         <is>
-          <t>interno</t>
+          <t>imprensa</t>
         </is>
       </c>
       <c r="W40" s="6" t="inlineStr">
         <is>
-          <t>https://www.imovelnacidade.com/destaque/mb-construtora/</t>
+          <t>https://www.bergengenharia.com.br</t>
         </is>
       </c>
       <c r="X40" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>27/04/2026</t>
         </is>
       </c>
       <c r="Y40" s="7" t="inlineStr">
         <is>
-          <t>DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 06/2023 confirmado internamente. Casa duplex 3Q, 136m², R$906.870. Produto horizontal Eldorado/Turú. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Tabela ABR/2026 (Berg Engenharia). 4 tipologias (1-4) com áreas similares 135,32 / 135,83 m². Lançamento 04/2024 estimado pela pasta. Conclusão: 30/04/2027 (T-36 perfeito). Tipo 3 (135,32m²): apto 103 disponível R$ 1.932.400. Tipo 4 (135,83m²): apto 104 disponível R$ 1.944.500, demais (204-1004) VENDIDOS = 9 vendidos no Tipo 4 → estoque concentrado em 1 unidade visível. Apto 704 tem 3 vagas (diferencial). Correção INCC. Histórico Berg: Montparnasse, Golden Tower, Peninsula Mall, Monte Olimpo, Monte Fuji.</t>
         </is>
       </c>
     </row>
     <row r="41" ht="52" customHeight="1">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t>Alfa Engenharia</t>
+          <t>Treviso</t>
         </is>
       </c>
       <c r="B41" s="12" t="inlineStr">
         <is>
-          <t>Legacy Residence</t>
+          <t>Altos do São Francisco</t>
         </is>
       </c>
       <c r="C41" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Bairro São Francisco, São Luís - MA</t>
         </is>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
-          <t>Ponta d'Areia</t>
+          <t>São Francisco</t>
         </is>
       </c>
       <c r="E41" s="12" t="inlineStr">
@@ -4320,93 +4314,109 @@
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Médio-alto</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Lançamento</t>
-        </is>
-      </c>
-      <c r="H41" s="12" t="n"/>
+          <t>Entregue</t>
+        </is>
+      </c>
+      <c r="H41" s="12" t="n">
+        <v>26</v>
+      </c>
       <c r="I41" s="12" t="inlineStr">
         <is>
-          <t>~2023</t>
+          <t>01/2024 ⚠ T-36</t>
         </is>
       </c>
       <c r="J41" s="12" t="inlineStr">
         <is>
-          <t>10/2027</t>
-        </is>
-      </c>
-      <c r="K41" s="14" t="n"/>
-      <c r="L41" s="14" t="n"/>
-      <c r="M41" s="14" t="n"/>
+          <t>Pronto</t>
+        </is>
+      </c>
+      <c r="K41" s="14" t="n">
+        <v>57.93</v>
+      </c>
+      <c r="L41" s="14" t="n">
+        <v>67.15000000000001</v>
+      </c>
+      <c r="M41" s="14" t="n">
+        <v>62.54000000000001</v>
+      </c>
       <c r="N41" s="13" t="inlineStr">
         <is>
-          <t>4 suítes</t>
-        </is>
-      </c>
-      <c r="O41" s="15" t="n"/>
-      <c r="P41" s="15" t="n"/>
-      <c r="Q41" s="15" t="n"/>
-      <c r="R41" s="15" t="n"/>
+          <t>2-3Q (1 ou 2 vagas)</t>
+        </is>
+      </c>
+      <c r="O41" s="15" t="n">
+        <v>495800</v>
+      </c>
+      <c r="P41" s="15" t="n">
+        <v>761700</v>
+      </c>
+      <c r="Q41" s="15" t="n">
+        <v>10053.56571794052</v>
+      </c>
+      <c r="R41" s="15" t="n">
+        <v>16347500</v>
+      </c>
       <c r="S41" s="16" t="n"/>
       <c r="T41" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="U41" s="12" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela</t>
         </is>
       </c>
       <c r="V41" s="12" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>pendente</t>
         </is>
       </c>
       <c r="W41" s="12" t="inlineStr">
         <is>
-          <t>https://www.alfaengenharia.com.br</t>
+          <t>https://trevisoengenharia.com.br</t>
         </is>
       </c>
       <c r="X41" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y41" s="13" t="inlineStr">
         <is>
-          <t>13 opções de lazer, elevador privativo. Book local (375MB) + site oficial. Sem ticket público.</t>
+          <t>IMÓVEL PRONTO. 26+ unid na tab ABR/26 (VGV R$ 15,8M). Tipos: 57,93 m² (1 vaga) e 67,15 m² (2 vagas). Ticket R$ 495k–762k (méd R$ 607k). R$/m² pond R$ 10.042. Estoque amplo. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="42" ht="52" customHeight="1">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>Castelucci</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>Residencial Ana Vitória</t>
+          <t>Edifício Dom Ricardo</t>
         </is>
       </c>
       <c r="C42" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Araçagy, São Luís - MA</t>
+          <t>Rua dos Rouxinóis, 8, Jardim Renascença, São Luís - MA</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>Araçagy</t>
+          <t>Jardim Renascença</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Horizontal</t>
+          <t>Vertical</t>
         </is>
       </c>
       <c r="F42" s="6" t="inlineStr">
@@ -4416,13 +4426,13 @@
       </c>
       <c r="G42" s="6" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
+          <t>Últimas unidades</t>
         </is>
       </c>
       <c r="H42" s="6" t="n"/>
       <c r="I42" s="6" t="inlineStr">
         <is>
-          <t>~2023</t>
+          <t>12/2023</t>
         </is>
       </c>
       <c r="J42" s="6" t="inlineStr">
@@ -4430,9 +4440,15 @@
           <t>—</t>
         </is>
       </c>
-      <c r="K42" s="8" t="n"/>
-      <c r="L42" s="8" t="n"/>
-      <c r="M42" s="8" t="n"/>
+      <c r="K42" s="8" t="n">
+        <v>71</v>
+      </c>
+      <c r="L42" s="8" t="n">
+        <v>85</v>
+      </c>
+      <c r="M42" s="8" t="n">
+        <v>78</v>
+      </c>
       <c r="N42" s="7" t="inlineStr">
         <is>
           <t>2-3Q</t>
@@ -4442,52 +4458,54 @@
       <c r="P42" s="9" t="n"/>
       <c r="Q42" s="9" t="n"/>
       <c r="R42" s="9" t="n"/>
-      <c r="S42" s="10" t="n"/>
+      <c r="S42" s="10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
       <c r="T42" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>agregador</t>
         </is>
       </c>
       <c r="U42" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>agregador</t>
         </is>
       </c>
       <c r="V42" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>interno</t>
         </is>
       </c>
       <c r="W42" s="6" t="inlineStr">
         <is>
-          <t>https://construtoracastelucci.com.br</t>
+          <t>https://www.imeu.com.br/empreendimento/dom-ricardo-apartamentos-sao-luis-2-a-3-quartos-71-a-85-m/19044585-MIM</t>
         </is>
       </c>
       <c r="X42" s="6" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y42" s="7" t="inlineStr">
         <is>
-          <t>Apartamentos 2-3Q Araçagy. Site oficial Castelucci.</t>
+          <t>DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 12/2023 confirmado internamente. Próximo à Praça da Lagoa (Foguete). 'Sucesso de vendas, 6 unidades disponíveis' (IG jan/2025). Estoque estimado ≤6%. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
     <row r="43" ht="52" customHeight="1">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t>Delman</t>
+          <t>Alfa Engenharia</t>
         </is>
       </c>
       <c r="B43" s="12" t="inlineStr">
         <is>
-          <t>Azimuth</t>
+          <t>LIV Residence</t>
         </is>
       </c>
       <c r="C43" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
+          <t>Rua Aziz Heluy, S/N, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D43" s="12" t="inlineStr">
@@ -4502,74 +4520,56 @@
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>Luxo</t>
+          <t>Alto</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Últimas unidades</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="n">
-        <v>30</v>
-      </c>
+          <t>Lançamento</t>
+        </is>
+      </c>
+      <c r="H43" s="12" t="n"/>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>~2023</t>
+          <t>07/2023</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>10/2026</t>
-        </is>
-      </c>
-      <c r="K43" s="14" t="n">
-        <v>196.62</v>
-      </c>
-      <c r="L43" s="14" t="n">
-        <v>196.62</v>
-      </c>
-      <c r="M43" s="14" t="n">
-        <v>196.62</v>
-      </c>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="K43" s="14" t="n"/>
+      <c r="L43" s="14" t="n"/>
+      <c r="M43" s="14" t="n"/>
       <c r="N43" s="13" t="inlineStr">
         <is>
           <t>3 suítes</t>
         </is>
       </c>
-      <c r="O43" s="15" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="P43" s="15" t="n">
-        <v>3600000</v>
-      </c>
-      <c r="Q43" s="15" t="n">
-        <v>18309.4293561184</v>
-      </c>
-      <c r="R43" s="15" t="n">
-        <v>108000000</v>
-      </c>
-      <c r="S43" s="16" t="n">
-        <v>0.9666666666666667</v>
-      </c>
+      <c r="O43" s="15" t="n"/>
+      <c r="P43" s="15" t="n"/>
+      <c r="Q43" s="15" t="n"/>
+      <c r="R43" s="15" t="n"/>
+      <c r="S43" s="16" t="n"/>
       <c r="T43" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="U43" s="12" t="inlineStr">
         <is>
-          <t>tabela_local</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V43" s="12" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W43" s="12" t="inlineStr">
         <is>
-          <t>https://www.delman.com.br</t>
+          <t>https://www.alfaengenharia.com.br</t>
         </is>
       </c>
       <c r="X43" s="12" t="inlineStr">
@@ -4579,29 +4579,29 @@
       </c>
       <c r="Y43" s="13" t="inlineStr">
         <is>
-          <t>Tabela 04/2026: 1 apto (901) de 30. ≈97% vendido. Lançamento confirmado 2023 pela imprensa.</t>
+          <t>1º Housi do MA. Book local + site Alfa. Sem tabela comercial.</t>
         </is>
       </c>
     </row>
     <row r="44" ht="52" customHeight="1">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>Ergus</t>
+          <t>Delman</t>
         </is>
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>Nexus Renascença</t>
+          <t>Azimuth</t>
         </is>
       </c>
       <c r="C44" s="7" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Renascença, São Luís - MA</t>
+          <t>Endereço não localizado, Ponta d'Areia, São Luís - MA</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>Renascença</t>
+          <t>Ponta d'Areia</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
@@ -4611,52 +4611,64 @@
       </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>Luxo</t>
         </is>
       </c>
       <c r="G44" s="6" t="inlineStr">
         <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H44" s="6" t="n"/>
+          <t>Últimas unidades</t>
+        </is>
+      </c>
+      <c r="H44" s="6" t="n">
+        <v>30</v>
+      </c>
       <c r="I44" s="6" t="inlineStr">
         <is>
-          <t>~2023</t>
+          <t>07/2023</t>
         </is>
       </c>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10/2026</t>
         </is>
       </c>
       <c r="K44" s="8" t="n">
-        <v>33</v>
+        <v>196.62</v>
       </c>
       <c r="L44" s="8" t="n">
-        <v>94</v>
+        <v>196.62</v>
       </c>
       <c r="M44" s="8" t="n">
-        <v>63.5</v>
+        <v>196.62</v>
       </c>
       <c r="N44" s="7" t="inlineStr">
         <is>
-          <t>Studio a 2Q</t>
-        </is>
-      </c>
-      <c r="O44" s="9" t="n"/>
-      <c r="P44" s="9" t="n"/>
-      <c r="Q44" s="9" t="n"/>
-      <c r="R44" s="9" t="n"/>
-      <c r="S44" s="10" t="n"/>
+          <t>3 suítes</t>
+        </is>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="P44" s="9" t="n">
+        <v>3600000</v>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>18309.4293561184</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>108000000</v>
+      </c>
+      <c r="S44" s="10" t="n">
+        <v>0.9666666666666667</v>
+      </c>
       <c r="T44" s="6" t="inlineStr">
         <is>
-          <t>site_oficial</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="U44" s="6" t="inlineStr">
         <is>
-          <t>N/A</t>
+          <t>tabela_local</t>
         </is>
       </c>
       <c r="V44" s="6" t="inlineStr">
@@ -4666,7 +4678,7 @@
       </c>
       <c r="W44" s="6" t="inlineStr">
         <is>
-          <t>https://www.ergus.com.br</t>
+          <t>https://www.delman.com.br</t>
         </is>
       </c>
       <c r="X44" s="6" t="inlineStr">
@@ -4676,106 +4688,110 @@
       </c>
       <c r="Y44" s="7" t="inlineStr">
         <is>
-          <t>Complexo 10mil m² multi-produto (residencial + comercial + Open Mall). Book local + site oficial.</t>
+          <t>Tabela 04/2026: 1 apto (901) de 30. ≈97% vendido. Lançamento confirmado 2023 pela imprensa.</t>
         </is>
       </c>
     </row>
     <row r="45" ht="52" customHeight="1">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t>MB Engenharia</t>
+          <t>DOM Incorporação</t>
         </is>
       </c>
       <c r="B45" s="12" t="inlineStr">
         <is>
-          <t>Condomínio Prime Cohama</t>
+          <t>Dom Antônio</t>
         </is>
       </c>
       <c r="C45" s="13" t="inlineStr">
         <is>
-          <t>Endereço não localizado, Cohama, São Luís - MA</t>
+          <t>Endereço não localizado, Jardim Eldorado (Turú), São Luís - MA</t>
         </is>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
-          <t>Cohama</t>
+          <t>Jardim Eldorado</t>
         </is>
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
         <is>
+          <t>Médio</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="n"/>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>06/2023</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>Em comercialização</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>22</v>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>~2023</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="K45" s="14" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="L45" s="14" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="M45" s="14" t="n">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="N45" s="13" t="inlineStr">
         <is>
-          <t>Casas duplex</t>
-        </is>
-      </c>
-      <c r="O45" s="15" t="n"/>
-      <c r="P45" s="15" t="n"/>
-      <c r="Q45" s="15" t="n"/>
+          <t>3Q casas duplex</t>
+        </is>
+      </c>
+      <c r="O45" s="15" t="n">
+        <v>906870</v>
+      </c>
+      <c r="P45" s="15" t="n">
+        <v>906870</v>
+      </c>
+      <c r="Q45" s="15" t="n">
+        <v>6668.161764705882</v>
+      </c>
       <c r="R45" s="15" t="n"/>
       <c r="S45" s="16" t="n"/>
       <c r="T45" s="12" t="inlineStr">
         <is>
+          <t>agregador</t>
+        </is>
+      </c>
+      <c r="U45" s="12" t="inlineStr">
+        <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="U45" s="12" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
       <c r="V45" s="12" t="inlineStr">
         <is>
-          <t>imprensa</t>
+          <t>interno</t>
         </is>
       </c>
       <c r="W45" s="12" t="inlineStr">
         <is>
-          <t>https://www.instagram.com/mbengenharia.br/</t>
+          <t>https://www.imovelnacidade.com/destaque/mb-construtora/</t>
         </is>
       </c>
       <c r="X45" s="12" t="inlineStr">
         <is>
-          <t>14/04/2026</t>
+          <t>23/04/2026</t>
         </is>
       </c>
       <c r="Y45" s="13" t="inlineStr">
         <is>
-          <t>22 casas duplex 140m² — produto horizontal diferenciado. Pré-lançamento anunciado 2023, hoje em comercialização.</t>
+          <t>DOM Incorporação com MB Engenharia como sócia (empreendimento conjunto). Lançamento 06/2023 confirmado internamente. Casa duplex 3Q, 136m², R$906.870. Produto horizontal Eldorado/Turú. [reconstituído da v4.16 em 25/04/2026]</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4834,7 @@
       <c r="H46" s="6" t="n"/>
       <c r="I46" s="6" t="inlineStr">
         <is>
-          <t>~2023</t>
+          <t>12/2022</t>
         </is>
       </c>
       <c r="J46" s="6" t="inlineStr">
@@ -5125,7 +5141,7 @@
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>02/2019</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
@@ -5186,107 +5202,91 @@
     <row r="50" ht="52" customHeight="1">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>Treviso</t>
+          <t>Castelucci</t>
         </is>
       </c>
       <c r="B50" s="6" t="inlineStr">
         <is>
-          <t>Altos do São Francisco</t>
+          <t>Residencial Ana Vitória</t>
         </is>
       </c>
       <c r="C50" s="7" t="inlineStr">
         <is>
-          <t>Bairro São Francisco, São Luís - MA</t>
+          <t>Endereço não localizado, Araçagy, São Luís - MA</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>São Francisco</t>
+          <t>Araçagy</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Vertical</t>
+          <t>Horizontal</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>Médio-alto</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G50" s="6" t="inlineStr">
         <is>
-          <t>Entregue</t>
-        </is>
-      </c>
-      <c r="H50" s="6" t="n">
-        <v>26</v>
-      </c>
+          <t>Em comercialização</t>
+        </is>
+      </c>
+      <c r="H50" s="6" t="n"/>
       <c r="I50" s="6" t="inlineStr">
         <is>
+          <t>01/2018</t>
+        </is>
+      </c>
+      <c r="J50" s="6" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J50" s="6" t="inlineStr">
-        <is>
-          <t>Pronto</t>
-        </is>
-      </c>
-      <c r="K50" s="8" t="n">
-        <v>57.93</v>
-      </c>
-      <c r="L50" s="8" t="n">
-        <v>67.15000000000001</v>
-      </c>
-      <c r="M50" s="8" t="n">
-        <v>62.54000000000001</v>
-      </c>
+      <c r="K50" s="8" t="n"/>
+      <c r="L50" s="8" t="n"/>
+      <c r="M50" s="8" t="n"/>
       <c r="N50" s="7" t="inlineStr">
         <is>
-          <t>2-3Q (1 ou 2 vagas)</t>
-        </is>
-      </c>
-      <c r="O50" s="9" t="n">
-        <v>495800</v>
-      </c>
-      <c r="P50" s="9" t="n">
-        <v>761700</v>
-      </c>
-      <c r="Q50" s="9" t="n">
-        <v>10053.56571794052</v>
-      </c>
-      <c r="R50" s="9" t="n">
-        <v>16347500</v>
-      </c>
+          <t>2-3Q</t>
+        </is>
+      </c>
+      <c r="O50" s="9" t="n"/>
+      <c r="P50" s="9" t="n"/>
+      <c r="Q50" s="9" t="n"/>
+      <c r="R50" s="9" t="n"/>
       <c r="S50" s="10" t="n"/>
       <c r="T50" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="U50" s="6" t="inlineStr">
         <is>
-          <t>tabela</t>
+          <t>N/A</t>
         </is>
       </c>
       <c r="V50" s="6" t="inlineStr">
         <is>
-          <t>pendente</t>
+          <t>site_oficial</t>
         </is>
       </c>
       <c r="W50" s="6" t="inlineStr">
         <is>
-          <t>https://trevisoengenharia.com.br</t>
+          <t>https://construtoracastelucci.com.br</t>
         </is>
       </c>
       <c r="X50" s="6" t="inlineStr">
         <is>
-          <t>23/04/2026</t>
+          <t>14/04/2026</t>
         </is>
       </c>
       <c r="Y50" s="7" t="inlineStr">
         <is>
-          <t>IMÓVEL PRONTO. 26+ unid na tab ABR/26 (VGV R$ 15,8M). Tipos: 57,93 m² (1 vaga) e 67,15 m² (2 vagas). Ticket R$ 495k–762k (méd R$ 607k). R$/m² pond R$ 10.042. Estoque amplo. [reconstituído da v4.16 em 25/04/2026]</t>
+          <t>Apartamentos 2-3Q Araçagy. Site oficial Castelucci.</t>
         </is>
       </c>
     </row>
@@ -5468,10 +5468,10 @@
         <v>659025000</v>
       </c>
       <c r="D6" s="9" t="n">
-        <v>225900000</v>
+        <v>56400000</v>
       </c>
       <c r="E6" s="9" t="n">
-        <v>106875000</v>
+        <v>276375000</v>
       </c>
       <c r="F6" s="9" t="n">
         <v>128250000</v>
@@ -5529,7 +5529,7 @@
         <v>259647500</v>
       </c>
       <c r="D7" s="15" t="n">
-        <v>0</v>
+        <v>16347500</v>
       </c>
       <c r="E7" s="15" t="n">
         <v>243300000</v>
